--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N285"/>
+  <dimension ref="A1:N289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6181,7 +6181,7 @@
         <v>155</v>
       </c>
       <c r="B131" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C131" t="n">
         <v>155</v>
@@ -6225,7 +6225,7 @@
         <v>155</v>
       </c>
       <c r="B132" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C132" t="n">
         <v>155</v>
@@ -6269,7 +6269,7 @@
         <v>155</v>
       </c>
       <c r="B133" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C133" t="n">
         <v>155</v>
@@ -6313,7 +6313,7 @@
         <v>155</v>
       </c>
       <c r="B134" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C134" t="n">
         <v>155</v>
@@ -6357,7 +6357,7 @@
         <v>155</v>
       </c>
       <c r="B135" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C135" t="n">
         <v>155</v>
@@ -6401,43 +6401,43 @@
         <v>155</v>
       </c>
       <c r="B136" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C136" t="n">
         <v>155</v>
       </c>
       <c r="D136" t="n">
-        <v>88.1572210064911</v>
+        <v>88.42860693509897</v>
       </c>
       <c r="E136" t="n">
-        <v>440.16</v>
+        <v>441.125</v>
       </c>
       <c r="F136" t="n">
-        <v>167.3291352543095</v>
+        <v>166.9630879536115</v>
       </c>
       <c r="G136" t="n">
-        <v>32646.77412710944</v>
+        <v>31283.77216678231</v>
       </c>
       <c r="H136" t="n">
-        <v>-8913.716273844328</v>
+        <v>-8706.335596188268</v>
       </c>
       <c r="I136" t="n">
-        <v>4.7</v>
+        <v>4.735</v>
       </c>
       <c r="J136" t="n">
-        <v>10.155</v>
+        <v>10.25</v>
       </c>
       <c r="K136" t="n">
-        <v>1.73</v>
+        <v>1.755</v>
       </c>
       <c r="L136" t="n">
-        <v>2.545</v>
+        <v>2.58</v>
       </c>
       <c r="M136" t="n">
-        <v>300.1702780782407</v>
+        <v>300.1675419478739</v>
       </c>
       <c r="N136" t="n">
-        <v>6.871714566438358</v>
+        <v>6.77824024391566</v>
       </c>
     </row>
     <row r="137">
@@ -6445,43 +6445,43 @@
         <v>155</v>
       </c>
       <c r="B137" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C137" t="n">
         <v>155</v>
       </c>
       <c r="D137" t="n">
-        <v>88.17159808944842</v>
+        <v>88.40873974939892</v>
       </c>
       <c r="E137" t="n">
-        <v>440.02</v>
+        <v>441.255</v>
       </c>
       <c r="F137" t="n">
-        <v>167.38237392286</v>
+        <v>166.9138982527946</v>
       </c>
       <c r="G137" t="n">
-        <v>32611.25635694649</v>
+        <v>31324.41639119873</v>
       </c>
       <c r="H137" t="n">
-        <v>-8910.745193147051</v>
+        <v>-8693.338280445179</v>
       </c>
       <c r="I137" t="n">
-        <v>4.7</v>
+        <v>4.735</v>
       </c>
       <c r="J137" t="n">
-        <v>10.155</v>
+        <v>10.25</v>
       </c>
       <c r="K137" t="n">
-        <v>1.73</v>
+        <v>1.755</v>
       </c>
       <c r="L137" t="n">
-        <v>2.545</v>
+        <v>2.58</v>
       </c>
       <c r="M137" t="n">
-        <v>300.1702780782455</v>
+        <v>300.1675419478711</v>
       </c>
       <c r="N137" t="n">
-        <v>6.871714566438371</v>
+        <v>6.778240243915617</v>
       </c>
     </row>
     <row r="138">
@@ -6489,7 +6489,7 @@
         <v>155</v>
       </c>
       <c r="B138" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C138" t="n">
         <v>155</v>
@@ -6533,7 +6533,7 @@
         <v>155</v>
       </c>
       <c r="B139" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C139" t="n">
         <v>155</v>
@@ -6577,7 +6577,7 @@
         <v>155</v>
       </c>
       <c r="B140" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C140" t="n">
         <v>155</v>
@@ -6621,7 +6621,7 @@
         <v>155</v>
       </c>
       <c r="B141" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C141" t="n">
         <v>155</v>
@@ -6665,43 +6665,43 @@
         <v>155</v>
       </c>
       <c r="B142" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C142" t="n">
         <v>155</v>
       </c>
       <c r="D142" t="n">
-        <v>87.86419645306405</v>
+        <v>88.1572210064911</v>
       </c>
       <c r="E142" t="n">
-        <v>439.295</v>
+        <v>440.16</v>
       </c>
       <c r="F142" t="n">
-        <v>167.6586170421627</v>
+        <v>167.3291352543095</v>
       </c>
       <c r="G142" t="n">
-        <v>34031.75298279929</v>
+        <v>32646.77412710944</v>
       </c>
       <c r="H142" t="n">
-        <v>-9128.640627802281</v>
+        <v>-8913.716273844328</v>
       </c>
       <c r="I142" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="J142" t="n">
-        <v>10.065</v>
+        <v>10.155</v>
       </c>
       <c r="K142" t="n">
-        <v>1.715</v>
+        <v>1.73</v>
       </c>
       <c r="L142" t="n">
-        <v>2.515</v>
+        <v>2.545</v>
       </c>
       <c r="M142" t="n">
-        <v>300.1730141214379</v>
+        <v>300.1702780782407</v>
       </c>
       <c r="N142" t="n">
-        <v>6.965076109757545</v>
+        <v>6.871714566438358</v>
       </c>
     </row>
     <row r="143">
@@ -6709,43 +6709,43 @@
         <v>155</v>
       </c>
       <c r="B143" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C143" t="n">
         <v>155</v>
       </c>
       <c r="D143" t="n">
-        <v>87.87378211434536</v>
+        <v>88.17159808944842</v>
       </c>
       <c r="E143" t="n">
-        <v>439.095</v>
+        <v>440.02</v>
       </c>
       <c r="F143" t="n">
-        <v>167.7349825744699</v>
+        <v>167.38237392286</v>
       </c>
       <c r="G143" t="n">
-        <v>34006.71847726913</v>
+        <v>32611.25635694649</v>
       </c>
       <c r="H143" t="n">
-        <v>-9131.765675145727</v>
+        <v>-8910.745193147051</v>
       </c>
       <c r="I143" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="J143" t="n">
-        <v>10.065</v>
+        <v>10.155</v>
       </c>
       <c r="K143" t="n">
-        <v>1.715</v>
+        <v>1.73</v>
       </c>
       <c r="L143" t="n">
-        <v>2.515</v>
+        <v>2.545</v>
       </c>
       <c r="M143" t="n">
-        <v>300.1730141214466</v>
+        <v>300.1702780782455</v>
       </c>
       <c r="N143" t="n">
-        <v>6.965076109757529</v>
+        <v>6.871714566438371</v>
       </c>
     </row>
     <row r="144">
@@ -6753,43 +6753,43 @@
         <v>155</v>
       </c>
       <c r="B144" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C144" t="n">
         <v>155</v>
       </c>
       <c r="D144" t="n">
-        <v>87.86419645306405</v>
+        <v>88.1572210064911</v>
       </c>
       <c r="E144" t="n">
-        <v>439.295</v>
+        <v>440.16</v>
       </c>
       <c r="F144" t="n">
-        <v>167.6586170421627</v>
+        <v>167.3291352543095</v>
       </c>
       <c r="G144" t="n">
-        <v>34031.75298279929</v>
+        <v>32646.77412710944</v>
       </c>
       <c r="H144" t="n">
-        <v>-9128.640627802281</v>
+        <v>-8913.716273844328</v>
       </c>
       <c r="I144" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="J144" t="n">
-        <v>10.065</v>
+        <v>10.155</v>
       </c>
       <c r="K144" t="n">
-        <v>1.715</v>
+        <v>1.73</v>
       </c>
       <c r="L144" t="n">
-        <v>2.515</v>
+        <v>2.545</v>
       </c>
       <c r="M144" t="n">
-        <v>300.1730141214379</v>
+        <v>300.1702780782407</v>
       </c>
       <c r="N144" t="n">
-        <v>6.965076109757545</v>
+        <v>6.871714566438358</v>
       </c>
     </row>
     <row r="145">
@@ -6797,43 +6797,43 @@
         <v>155</v>
       </c>
       <c r="B145" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C145" t="n">
         <v>155</v>
       </c>
       <c r="D145" t="n">
-        <v>87.87378211434536</v>
+        <v>88.17159808944842</v>
       </c>
       <c r="E145" t="n">
-        <v>439.095</v>
+        <v>440.02</v>
       </c>
       <c r="F145" t="n">
-        <v>167.7349825744699</v>
+        <v>167.38237392286</v>
       </c>
       <c r="G145" t="n">
-        <v>34006.71847726913</v>
+        <v>32611.25635694649</v>
       </c>
       <c r="H145" t="n">
-        <v>-9131.765675145727</v>
+        <v>-8910.745193147051</v>
       </c>
       <c r="I145" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="J145" t="n">
-        <v>10.065</v>
+        <v>10.155</v>
       </c>
       <c r="K145" t="n">
-        <v>1.715</v>
+        <v>1.73</v>
       </c>
       <c r="L145" t="n">
-        <v>2.515</v>
+        <v>2.545</v>
       </c>
       <c r="M145" t="n">
-        <v>300.1730141214466</v>
+        <v>300.1702780782455</v>
       </c>
       <c r="N145" t="n">
-        <v>6.965076109757529</v>
+        <v>6.871714566438371</v>
       </c>
     </row>
     <row r="146">
@@ -6841,7 +6841,7 @@
         <v>155</v>
       </c>
       <c r="B146" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C146" t="n">
         <v>155</v>
@@ -6885,7 +6885,7 @@
         <v>155</v>
       </c>
       <c r="B147" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C147" t="n">
         <v>155</v>
@@ -6929,7 +6929,7 @@
         <v>155</v>
       </c>
       <c r="B148" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C148" t="n">
         <v>155</v>
@@ -6973,7 +6973,7 @@
         <v>155</v>
       </c>
       <c r="B149" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C149" t="n">
         <v>155</v>
@@ -7017,43 +7017,43 @@
         <v>155</v>
       </c>
       <c r="B150" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C150" t="n">
         <v>155</v>
       </c>
       <c r="D150" t="n">
-        <v>87.56131247206589</v>
+        <v>87.86419645306405</v>
       </c>
       <c r="E150" t="n">
-        <v>438.605</v>
+        <v>439.295</v>
       </c>
       <c r="F150" t="n">
-        <v>167.9223724616383</v>
+        <v>167.6586170421627</v>
       </c>
       <c r="G150" t="n">
-        <v>35430.49794246393</v>
+        <v>34031.75298279929</v>
       </c>
       <c r="H150" t="n">
-        <v>-9317.787773346581</v>
+        <v>-9128.640627802281</v>
       </c>
       <c r="I150" t="n">
-        <v>4.635</v>
+        <v>4.67</v>
       </c>
       <c r="J150" t="n">
-        <v>9.98</v>
+        <v>10.065</v>
       </c>
       <c r="K150" t="n">
-        <v>1.69</v>
+        <v>1.715</v>
       </c>
       <c r="L150" t="n">
-        <v>2.48</v>
+        <v>2.515</v>
       </c>
       <c r="M150" t="n">
-        <v>300.1756746796096</v>
+        <v>300.1730141214379</v>
       </c>
       <c r="N150" t="n">
-        <v>7.058356217954087</v>
+        <v>6.965076109757545</v>
       </c>
     </row>
     <row r="151">
@@ -7061,43 +7061,43 @@
         <v>155</v>
       </c>
       <c r="B151" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C151" t="n">
         <v>155</v>
       </c>
       <c r="D151" t="n">
-        <v>87.55156918335366</v>
+        <v>87.87378211434536</v>
       </c>
       <c r="E151" t="n">
-        <v>438.755</v>
+        <v>439.095</v>
       </c>
       <c r="F151" t="n">
-        <v>167.864963757762</v>
+        <v>167.7349825744699</v>
       </c>
       <c r="G151" t="n">
-        <v>35453.46463988696</v>
+        <v>34006.71847726913</v>
       </c>
       <c r="H151" t="n">
-        <v>-9311.860505554532</v>
+        <v>-9131.765675145727</v>
       </c>
       <c r="I151" t="n">
-        <v>4.635</v>
+        <v>4.67</v>
       </c>
       <c r="J151" t="n">
-        <v>9.98</v>
+        <v>10.065</v>
       </c>
       <c r="K151" t="n">
-        <v>1.69</v>
+        <v>1.715</v>
       </c>
       <c r="L151" t="n">
-        <v>2.48</v>
+        <v>2.515</v>
       </c>
       <c r="M151" t="n">
-        <v>300.1756746796139</v>
+        <v>300.1730141214466</v>
       </c>
       <c r="N151" t="n">
-        <v>7.058356217954033</v>
+        <v>6.965076109757529</v>
       </c>
     </row>
     <row r="152">
@@ -7105,43 +7105,43 @@
         <v>155</v>
       </c>
       <c r="B152" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C152" t="n">
         <v>155</v>
       </c>
       <c r="D152" t="n">
-        <v>87.56131247206589</v>
+        <v>87.86419645306405</v>
       </c>
       <c r="E152" t="n">
-        <v>438.605</v>
+        <v>439.295</v>
       </c>
       <c r="F152" t="n">
-        <v>167.9223724616383</v>
+        <v>167.6586170421627</v>
       </c>
       <c r="G152" t="n">
-        <v>35430.49794246393</v>
+        <v>34031.75298279929</v>
       </c>
       <c r="H152" t="n">
-        <v>-9317.787773346581</v>
+        <v>-9128.640627802281</v>
       </c>
       <c r="I152" t="n">
-        <v>4.635</v>
+        <v>4.67</v>
       </c>
       <c r="J152" t="n">
-        <v>9.98</v>
+        <v>10.065</v>
       </c>
       <c r="K152" t="n">
-        <v>1.69</v>
+        <v>1.715</v>
       </c>
       <c r="L152" t="n">
-        <v>2.48</v>
+        <v>2.515</v>
       </c>
       <c r="M152" t="n">
-        <v>300.1756746796096</v>
+        <v>300.1730141214379</v>
       </c>
       <c r="N152" t="n">
-        <v>7.058356217954087</v>
+        <v>6.965076109757545</v>
       </c>
     </row>
     <row r="153">
@@ -7149,43 +7149,43 @@
         <v>155</v>
       </c>
       <c r="B153" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C153" t="n">
         <v>155</v>
       </c>
       <c r="D153" t="n">
-        <v>87.55156918335366</v>
+        <v>87.87378211434536</v>
       </c>
       <c r="E153" t="n">
-        <v>438.755</v>
+        <v>439.095</v>
       </c>
       <c r="F153" t="n">
-        <v>167.864963757762</v>
+        <v>167.7349825744699</v>
       </c>
       <c r="G153" t="n">
-        <v>35453.46463988696</v>
+        <v>34006.71847726913</v>
       </c>
       <c r="H153" t="n">
-        <v>-9311.860505554532</v>
+        <v>-9131.765675145727</v>
       </c>
       <c r="I153" t="n">
-        <v>4.635</v>
+        <v>4.67</v>
       </c>
       <c r="J153" t="n">
-        <v>9.98</v>
+        <v>10.065</v>
       </c>
       <c r="K153" t="n">
-        <v>1.69</v>
+        <v>1.715</v>
       </c>
       <c r="L153" t="n">
-        <v>2.48</v>
+        <v>2.515</v>
       </c>
       <c r="M153" t="n">
-        <v>300.1756746796139</v>
+        <v>300.1730141214466</v>
       </c>
       <c r="N153" t="n">
-        <v>7.058356217954033</v>
+        <v>6.965076109757529</v>
       </c>
     </row>
     <row r="154">
@@ -7193,7 +7193,7 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C154" t="n">
         <v>155</v>
@@ -7237,7 +7237,7 @@
         <v>155</v>
       </c>
       <c r="B155" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C155" t="n">
         <v>155</v>
@@ -7281,7 +7281,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C156" t="n">
         <v>155</v>
@@ -7325,7 +7325,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C157" t="n">
         <v>155</v>
@@ -7366,178 +7366,178 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B158" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C158" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D158" t="n">
-        <v>88.5590272392397</v>
+        <v>87.56131247206589</v>
       </c>
       <c r="E158" t="n">
-        <v>439.425</v>
+        <v>438.605</v>
       </c>
       <c r="F158" t="n">
-        <v>167.6090167230742</v>
+        <v>167.9223724616383</v>
       </c>
       <c r="G158" t="n">
-        <v>30989.84645611935</v>
+        <v>35430.49794246393</v>
       </c>
       <c r="H158" t="n">
-        <v>-8721.838107503914</v>
+        <v>-9317.787773346581</v>
       </c>
       <c r="I158" t="n">
-        <v>4.685</v>
+        <v>4.635</v>
       </c>
       <c r="J158" t="n">
-        <v>10.08</v>
+        <v>9.98</v>
       </c>
       <c r="K158" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="L158" t="n">
-        <v>2.525</v>
+        <v>2.48</v>
       </c>
       <c r="M158" t="n">
-        <v>300.1655600854676</v>
+        <v>300.1756746796096</v>
       </c>
       <c r="N158" t="n">
-        <v>6.913555089282502</v>
+        <v>7.058356217954087</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B159" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C159" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D159" t="n">
-        <v>88.58239522615095</v>
+        <v>87.55156918335366</v>
       </c>
       <c r="E159" t="n">
-        <v>439.25</v>
+        <v>438.755</v>
       </c>
       <c r="F159" t="n">
-        <v>167.6757932237606</v>
+        <v>167.864963757762</v>
       </c>
       <c r="G159" t="n">
-        <v>30943.07200308655</v>
+        <v>35453.46463988696</v>
       </c>
       <c r="H159" t="n">
-        <v>-8735.419140556513</v>
+        <v>-9311.860505554532</v>
       </c>
       <c r="I159" t="n">
-        <v>4.685</v>
+        <v>4.635</v>
       </c>
       <c r="J159" t="n">
-        <v>10.08</v>
+        <v>9.98</v>
       </c>
       <c r="K159" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="L159" t="n">
-        <v>2.525</v>
+        <v>2.48</v>
       </c>
       <c r="M159" t="n">
-        <v>300.1655600854594</v>
+        <v>300.1756746796139</v>
       </c>
       <c r="N159" t="n">
-        <v>6.913555089282503</v>
+        <v>7.058356217954033</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B160" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C160" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D160" t="n">
-        <v>88.5590272392397</v>
+        <v>87.56131247206589</v>
       </c>
       <c r="E160" t="n">
-        <v>439.425</v>
+        <v>438.605</v>
       </c>
       <c r="F160" t="n">
-        <v>167.6090167230742</v>
+        <v>167.9223724616383</v>
       </c>
       <c r="G160" t="n">
-        <v>30989.84645611935</v>
+        <v>35430.49794246393</v>
       </c>
       <c r="H160" t="n">
-        <v>-8721.838107503914</v>
+        <v>-9317.787773346581</v>
       </c>
       <c r="I160" t="n">
-        <v>4.685</v>
+        <v>4.635</v>
       </c>
       <c r="J160" t="n">
-        <v>10.08</v>
+        <v>9.98</v>
       </c>
       <c r="K160" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="L160" t="n">
-        <v>2.525</v>
+        <v>2.48</v>
       </c>
       <c r="M160" t="n">
-        <v>300.1655600854676</v>
+        <v>300.1756746796096</v>
       </c>
       <c r="N160" t="n">
-        <v>6.913555089282502</v>
+        <v>7.058356217954087</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B161" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C161" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D161" t="n">
-        <v>88.58239522615095</v>
+        <v>87.55156918335366</v>
       </c>
       <c r="E161" t="n">
-        <v>439.25</v>
+        <v>438.755</v>
       </c>
       <c r="F161" t="n">
-        <v>167.6757932237606</v>
+        <v>167.864963757762</v>
       </c>
       <c r="G161" t="n">
-        <v>30943.07200308655</v>
+        <v>35453.46463988696</v>
       </c>
       <c r="H161" t="n">
-        <v>-8735.419140556513</v>
+        <v>-9311.860505554532</v>
       </c>
       <c r="I161" t="n">
-        <v>4.685</v>
+        <v>4.635</v>
       </c>
       <c r="J161" t="n">
-        <v>10.08</v>
+        <v>9.98</v>
       </c>
       <c r="K161" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="L161" t="n">
-        <v>2.525</v>
+        <v>2.48</v>
       </c>
       <c r="M161" t="n">
-        <v>300.1655600854594</v>
+        <v>300.1756746796139</v>
       </c>
       <c r="N161" t="n">
-        <v>6.913555089282503</v>
+        <v>7.058356217954033</v>
       </c>
     </row>
     <row r="162">
@@ -7545,7 +7545,7 @@
         <v>156</v>
       </c>
       <c r="B162" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C162" t="n">
         <v>156</v>
@@ -7589,7 +7589,7 @@
         <v>156</v>
       </c>
       <c r="B163" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C163" t="n">
         <v>156</v>
@@ -7633,7 +7633,7 @@
         <v>156</v>
       </c>
       <c r="B164" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C164" t="n">
         <v>156</v>
@@ -7677,7 +7677,7 @@
         <v>156</v>
       </c>
       <c r="B165" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C165" t="n">
         <v>156</v>
@@ -7721,43 +7721,43 @@
         <v>156</v>
       </c>
       <c r="B166" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C166" t="n">
         <v>156</v>
       </c>
       <c r="D166" t="n">
-        <v>88.33384417217431</v>
+        <v>88.5590272392397</v>
       </c>
       <c r="E166" t="n">
-        <v>438.26</v>
+        <v>439.425</v>
       </c>
       <c r="F166" t="n">
-        <v>168.0545616153354</v>
+        <v>167.6090167230742</v>
       </c>
       <c r="G166" t="n">
-        <v>32260.43827891049</v>
+        <v>30989.84645611935</v>
       </c>
       <c r="H166" t="n">
-        <v>-8941.536303254758</v>
+        <v>-8721.838107503914</v>
       </c>
       <c r="I166" t="n">
-        <v>4.65</v>
+        <v>4.685</v>
       </c>
       <c r="J166" t="n">
-        <v>9.99</v>
+        <v>10.08</v>
       </c>
       <c r="K166" t="n">
-        <v>1.695</v>
+        <v>1.72</v>
       </c>
       <c r="L166" t="n">
-        <v>2.495</v>
+        <v>2.525</v>
       </c>
       <c r="M166" t="n">
-        <v>300.1685927009576</v>
+        <v>300.1655600854676</v>
       </c>
       <c r="N166" t="n">
-        <v>7.013931759058152</v>
+        <v>6.913555089282502</v>
       </c>
     </row>
     <row r="167">
@@ -7765,43 +7765,43 @@
         <v>156</v>
       </c>
       <c r="B167" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C167" t="n">
         <v>156</v>
       </c>
       <c r="D167" t="n">
-        <v>88.34646613183374</v>
+        <v>88.58239522615095</v>
       </c>
       <c r="E167" t="n">
-        <v>438.11</v>
+        <v>439.25</v>
       </c>
       <c r="F167" t="n">
-        <v>168.1121000970917</v>
+        <v>167.6757932237606</v>
       </c>
       <c r="G167" t="n">
-        <v>32233.40577760103</v>
+        <v>30943.07200308655</v>
       </c>
       <c r="H167" t="n">
-        <v>-8950.660372826875</v>
+        <v>-8735.419140556513</v>
       </c>
       <c r="I167" t="n">
-        <v>4.65</v>
+        <v>4.685</v>
       </c>
       <c r="J167" t="n">
-        <v>9.99</v>
+        <v>10.08</v>
       </c>
       <c r="K167" t="n">
-        <v>1.695</v>
+        <v>1.72</v>
       </c>
       <c r="L167" t="n">
-        <v>2.495</v>
+        <v>2.525</v>
       </c>
       <c r="M167" t="n">
-        <v>300.1685927009574</v>
+        <v>300.1655600854594</v>
       </c>
       <c r="N167" t="n">
-        <v>7.013931759058106</v>
+        <v>6.913555089282503</v>
       </c>
     </row>
     <row r="168">
@@ -7809,43 +7809,43 @@
         <v>156</v>
       </c>
       <c r="B168" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C168" t="n">
         <v>156</v>
       </c>
       <c r="D168" t="n">
-        <v>88.33384417217431</v>
+        <v>88.5590272392397</v>
       </c>
       <c r="E168" t="n">
-        <v>438.26</v>
+        <v>439.425</v>
       </c>
       <c r="F168" t="n">
-        <v>168.0545616153354</v>
+        <v>167.6090167230742</v>
       </c>
       <c r="G168" t="n">
-        <v>32260.43827891049</v>
+        <v>30989.84645611935</v>
       </c>
       <c r="H168" t="n">
-        <v>-8941.536303254758</v>
+        <v>-8721.838107503914</v>
       </c>
       <c r="I168" t="n">
-        <v>4.65</v>
+        <v>4.685</v>
       </c>
       <c r="J168" t="n">
-        <v>9.99</v>
+        <v>10.08</v>
       </c>
       <c r="K168" t="n">
-        <v>1.695</v>
+        <v>1.72</v>
       </c>
       <c r="L168" t="n">
-        <v>2.495</v>
+        <v>2.525</v>
       </c>
       <c r="M168" t="n">
-        <v>300.1685927009576</v>
+        <v>300.1655600854676</v>
       </c>
       <c r="N168" t="n">
-        <v>7.013931759058152</v>
+        <v>6.913555089282502</v>
       </c>
     </row>
     <row r="169">
@@ -7853,43 +7853,43 @@
         <v>156</v>
       </c>
       <c r="B169" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C169" t="n">
         <v>156</v>
       </c>
       <c r="D169" t="n">
-        <v>88.34646613183374</v>
+        <v>88.58239522615095</v>
       </c>
       <c r="E169" t="n">
-        <v>438.11</v>
+        <v>439.25</v>
       </c>
       <c r="F169" t="n">
-        <v>168.1121000970917</v>
+        <v>167.6757932237606</v>
       </c>
       <c r="G169" t="n">
-        <v>32233.40577760103</v>
+        <v>30943.07200308655</v>
       </c>
       <c r="H169" t="n">
-        <v>-8950.660372826875</v>
+        <v>-8735.419140556513</v>
       </c>
       <c r="I169" t="n">
-        <v>4.65</v>
+        <v>4.685</v>
       </c>
       <c r="J169" t="n">
-        <v>9.99</v>
+        <v>10.08</v>
       </c>
       <c r="K169" t="n">
-        <v>1.695</v>
+        <v>1.72</v>
       </c>
       <c r="L169" t="n">
-        <v>2.495</v>
+        <v>2.525</v>
       </c>
       <c r="M169" t="n">
-        <v>300.1685927009574</v>
+        <v>300.1655600854594</v>
       </c>
       <c r="N169" t="n">
-        <v>7.013931759058106</v>
+        <v>6.913555089282503</v>
       </c>
     </row>
     <row r="170">
@@ -7897,7 +7897,7 @@
         <v>156</v>
       </c>
       <c r="B170" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C170" t="n">
         <v>156</v>
@@ -7941,7 +7941,7 @@
         <v>156</v>
       </c>
       <c r="B171" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C171" t="n">
         <v>156</v>
@@ -7985,7 +7985,7 @@
         <v>156</v>
       </c>
       <c r="B172" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C172" t="n">
         <v>156</v>
@@ -8029,7 +8029,7 @@
         <v>156</v>
       </c>
       <c r="B173" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C173" t="n">
         <v>156</v>
@@ -8073,43 +8073,43 @@
         <v>156</v>
       </c>
       <c r="B174" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C174" t="n">
         <v>156</v>
       </c>
       <c r="D174" t="n">
-        <v>88.04837552143277</v>
+        <v>88.33384417217431</v>
       </c>
       <c r="E174" t="n">
-        <v>437.435</v>
+        <v>438.26</v>
       </c>
       <c r="F174" t="n">
-        <v>168.3715115926638</v>
+        <v>168.0545616153354</v>
       </c>
       <c r="G174" t="n">
-        <v>33636.02049172654</v>
+        <v>32260.43827891049</v>
       </c>
       <c r="H174" t="n">
-        <v>-9164.803623340977</v>
+        <v>-8941.536303254758</v>
       </c>
       <c r="I174" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="J174" t="n">
-        <v>9.895</v>
+        <v>9.99</v>
       </c>
       <c r="K174" t="n">
-        <v>1.675</v>
+        <v>1.695</v>
       </c>
       <c r="L174" t="n">
-        <v>2.46</v>
+        <v>2.495</v>
       </c>
       <c r="M174" t="n">
-        <v>300.1714538846654</v>
+        <v>300.1685927009576</v>
       </c>
       <c r="N174" t="n">
-        <v>7.114210277511258</v>
+        <v>7.013931759058152</v>
       </c>
     </row>
     <row r="175">
@@ -8117,43 +8117,43 @@
         <v>156</v>
       </c>
       <c r="B175" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C175" t="n">
         <v>156</v>
       </c>
       <c r="D175" t="n">
-        <v>88.04659322617006</v>
+        <v>88.34646613183374</v>
       </c>
       <c r="E175" t="n">
-        <v>437.45</v>
+        <v>438.11</v>
       </c>
       <c r="F175" t="n">
-        <v>168.3657381953066</v>
+        <v>168.1121000970917</v>
       </c>
       <c r="G175" t="n">
-        <v>33640.68540373575</v>
+        <v>32233.40577760103</v>
       </c>
       <c r="H175" t="n">
-        <v>-9163.171980505342</v>
+        <v>-8950.660372826875</v>
       </c>
       <c r="I175" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="J175" t="n">
-        <v>9.895</v>
+        <v>9.99</v>
       </c>
       <c r="K175" t="n">
-        <v>1.675</v>
+        <v>1.695</v>
       </c>
       <c r="L175" t="n">
-        <v>2.46</v>
+        <v>2.495</v>
       </c>
       <c r="M175" t="n">
-        <v>300.1714538846628</v>
+        <v>300.1685927009574</v>
       </c>
       <c r="N175" t="n">
-        <v>7.114210277511289</v>
+        <v>7.013931759058106</v>
       </c>
     </row>
     <row r="176">
@@ -8161,43 +8161,43 @@
         <v>156</v>
       </c>
       <c r="B176" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C176" t="n">
         <v>156</v>
       </c>
       <c r="D176" t="n">
-        <v>88.04837552143277</v>
+        <v>88.33384417217431</v>
       </c>
       <c r="E176" t="n">
-        <v>437.435</v>
+        <v>438.26</v>
       </c>
       <c r="F176" t="n">
-        <v>168.3715115926638</v>
+        <v>168.0545616153354</v>
       </c>
       <c r="G176" t="n">
-        <v>33636.02049172654</v>
+        <v>32260.43827891049</v>
       </c>
       <c r="H176" t="n">
-        <v>-9164.803623340977</v>
+        <v>-8941.536303254758</v>
       </c>
       <c r="I176" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="J176" t="n">
-        <v>9.895</v>
+        <v>9.99</v>
       </c>
       <c r="K176" t="n">
-        <v>1.675</v>
+        <v>1.695</v>
       </c>
       <c r="L176" t="n">
-        <v>2.46</v>
+        <v>2.495</v>
       </c>
       <c r="M176" t="n">
-        <v>300.1714538846654</v>
+        <v>300.1685927009576</v>
       </c>
       <c r="N176" t="n">
-        <v>7.114210277511258</v>
+        <v>7.013931759058152</v>
       </c>
     </row>
     <row r="177">
@@ -8205,43 +8205,43 @@
         <v>156</v>
       </c>
       <c r="B177" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C177" t="n">
         <v>156</v>
       </c>
       <c r="D177" t="n">
-        <v>88.04659322617006</v>
+        <v>88.34646613183374</v>
       </c>
       <c r="E177" t="n">
-        <v>437.45</v>
+        <v>438.11</v>
       </c>
       <c r="F177" t="n">
-        <v>168.3657381953066</v>
+        <v>168.1121000970917</v>
       </c>
       <c r="G177" t="n">
-        <v>33640.68540373575</v>
+        <v>32233.40577760103</v>
       </c>
       <c r="H177" t="n">
-        <v>-9163.171980505342</v>
+        <v>-8950.660372826875</v>
       </c>
       <c r="I177" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="J177" t="n">
-        <v>9.895</v>
+        <v>9.99</v>
       </c>
       <c r="K177" t="n">
-        <v>1.675</v>
+        <v>1.695</v>
       </c>
       <c r="L177" t="n">
-        <v>2.46</v>
+        <v>2.495</v>
       </c>
       <c r="M177" t="n">
-        <v>300.1714538846628</v>
+        <v>300.1685927009574</v>
       </c>
       <c r="N177" t="n">
-        <v>7.114210277511289</v>
+        <v>7.013931759058106</v>
       </c>
     </row>
     <row r="178">
@@ -8249,7 +8249,7 @@
         <v>156</v>
       </c>
       <c r="B178" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C178" t="n">
         <v>156</v>
@@ -8293,7 +8293,7 @@
         <v>156</v>
       </c>
       <c r="B179" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C179" t="n">
         <v>156</v>
@@ -8337,7 +8337,7 @@
         <v>156</v>
       </c>
       <c r="B180" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C180" t="n">
         <v>156</v>
@@ -8381,7 +8381,7 @@
         <v>156</v>
       </c>
       <c r="B181" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C181" t="n">
         <v>156</v>
@@ -8425,43 +8425,43 @@
         <v>156</v>
       </c>
       <c r="B182" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C182" t="n">
         <v>156</v>
       </c>
       <c r="D182" t="n">
-        <v>87.80320469212297</v>
+        <v>88.04837552143277</v>
       </c>
       <c r="E182" t="n">
-        <v>436.505</v>
+        <v>437.435</v>
       </c>
       <c r="F182" t="n">
-        <v>168.7302371646072</v>
+        <v>168.3715115926638</v>
       </c>
       <c r="G182" t="n">
-        <v>34925.44109556412</v>
+        <v>33636.02049172654</v>
       </c>
       <c r="H182" t="n">
-        <v>-9359.421098322955</v>
+        <v>-9164.803623340977</v>
       </c>
       <c r="I182" t="n">
-        <v>4.585</v>
+        <v>4.62</v>
       </c>
       <c r="J182" t="n">
-        <v>9.805</v>
+        <v>9.895</v>
       </c>
       <c r="K182" t="n">
-        <v>1.655</v>
+        <v>1.675</v>
       </c>
       <c r="L182" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="M182" t="n">
-        <v>300.1745888736489</v>
+        <v>300.1714538846654</v>
       </c>
       <c r="N182" t="n">
-        <v>7.214413147291324</v>
+        <v>7.114210277511258</v>
       </c>
     </row>
     <row r="183">
@@ -8469,43 +8469,43 @@
         <v>156</v>
       </c>
       <c r="B183" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C183" t="n">
         <v>156</v>
       </c>
       <c r="D183" t="n">
-        <v>87.80383718901508</v>
+        <v>88.04659322617006</v>
       </c>
       <c r="E183" t="n">
-        <v>436.515</v>
+        <v>437.45</v>
       </c>
       <c r="F183" t="n">
-        <v>168.726371770814</v>
+        <v>168.3657381953066</v>
       </c>
       <c r="G183" t="n">
-        <v>34923.36026574186</v>
+        <v>33640.68540373575</v>
       </c>
       <c r="H183" t="n">
-        <v>-9360.308785346659</v>
+        <v>-9163.171980505342</v>
       </c>
       <c r="I183" t="n">
-        <v>4.585</v>
+        <v>4.62</v>
       </c>
       <c r="J183" t="n">
-        <v>9.805</v>
+        <v>9.895</v>
       </c>
       <c r="K183" t="n">
-        <v>1.655</v>
+        <v>1.675</v>
       </c>
       <c r="L183" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="M183" t="n">
-        <v>300.1745888736389</v>
+        <v>300.1714538846628</v>
       </c>
       <c r="N183" t="n">
-        <v>7.214413147291361</v>
+        <v>7.114210277511289</v>
       </c>
     </row>
     <row r="184">
@@ -8513,43 +8513,43 @@
         <v>156</v>
       </c>
       <c r="B184" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C184" t="n">
         <v>156</v>
       </c>
       <c r="D184" t="n">
-        <v>87.80320469212297</v>
+        <v>88.04837552143277</v>
       </c>
       <c r="E184" t="n">
-        <v>436.505</v>
+        <v>437.435</v>
       </c>
       <c r="F184" t="n">
-        <v>168.7302371646072</v>
+        <v>168.3715115926638</v>
       </c>
       <c r="G184" t="n">
-        <v>34925.44109556412</v>
+        <v>33636.02049172654</v>
       </c>
       <c r="H184" t="n">
-        <v>-9359.421098322955</v>
+        <v>-9164.803623340977</v>
       </c>
       <c r="I184" t="n">
-        <v>4.585</v>
+        <v>4.62</v>
       </c>
       <c r="J184" t="n">
-        <v>9.805</v>
+        <v>9.895</v>
       </c>
       <c r="K184" t="n">
-        <v>1.655</v>
+        <v>1.675</v>
       </c>
       <c r="L184" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="M184" t="n">
-        <v>300.1745888736489</v>
+        <v>300.1714538846654</v>
       </c>
       <c r="N184" t="n">
-        <v>7.214413147291324</v>
+        <v>7.114210277511258</v>
       </c>
     </row>
     <row r="185">
@@ -8557,43 +8557,43 @@
         <v>156</v>
       </c>
       <c r="B185" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C185" t="n">
         <v>156</v>
       </c>
       <c r="D185" t="n">
-        <v>87.80383718901508</v>
+        <v>88.04659322617006</v>
       </c>
       <c r="E185" t="n">
-        <v>436.515</v>
+        <v>437.45</v>
       </c>
       <c r="F185" t="n">
-        <v>168.726371770814</v>
+        <v>168.3657381953066</v>
       </c>
       <c r="G185" t="n">
-        <v>34923.36026574186</v>
+        <v>33640.68540373575</v>
       </c>
       <c r="H185" t="n">
-        <v>-9360.308785346659</v>
+        <v>-9163.171980505342</v>
       </c>
       <c r="I185" t="n">
-        <v>4.585</v>
+        <v>4.62</v>
       </c>
       <c r="J185" t="n">
-        <v>9.805</v>
+        <v>9.895</v>
       </c>
       <c r="K185" t="n">
-        <v>1.655</v>
+        <v>1.675</v>
       </c>
       <c r="L185" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="M185" t="n">
-        <v>300.1745888736389</v>
+        <v>300.1714538846628</v>
       </c>
       <c r="N185" t="n">
-        <v>7.214413147291361</v>
+        <v>7.114210277511289</v>
       </c>
     </row>
     <row r="186">
@@ -8601,7 +8601,7 @@
         <v>156</v>
       </c>
       <c r="B186" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C186" t="n">
         <v>156</v>
@@ -8645,7 +8645,7 @@
         <v>156</v>
       </c>
       <c r="B187" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C187" t="n">
         <v>156</v>
@@ -8689,7 +8689,7 @@
         <v>156</v>
       </c>
       <c r="B188" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C188" t="n">
         <v>156</v>
@@ -8733,7 +8733,7 @@
         <v>156</v>
       </c>
       <c r="B189" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C189" t="n">
         <v>156</v>
@@ -8774,178 +8774,178 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="B190" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C190" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="D190" t="n">
-        <v>89.18663858636465</v>
+        <v>87.80320469212297</v>
       </c>
       <c r="E190" t="n">
-        <v>444.19</v>
+        <v>436.505</v>
       </c>
       <c r="F190" t="n">
-        <v>165.8110091932211</v>
+        <v>168.7302371646072</v>
       </c>
       <c r="G190" t="n">
-        <v>24963.23633673095</v>
+        <v>34925.44109556412</v>
       </c>
       <c r="H190" t="n">
-        <v>-7442.612669115069</v>
+        <v>-9359.421098322955</v>
       </c>
       <c r="I190" t="n">
-        <v>4.63</v>
+        <v>4.585</v>
       </c>
       <c r="J190" t="n">
-        <v>10.22</v>
+        <v>9.805</v>
       </c>
       <c r="K190" t="n">
-        <v>1.65</v>
+        <v>1.655</v>
       </c>
       <c r="L190" t="n">
-        <v>2.425</v>
+        <v>2.43</v>
       </c>
       <c r="M190" t="n">
-        <v>300.0729606139864</v>
+        <v>300.1745888736489</v>
       </c>
       <c r="N190" t="n">
-        <v>7.263482551286738</v>
+        <v>7.214413147291324</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="B191" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C191" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="D191" t="n">
-        <v>89.18663858636465</v>
+        <v>87.80383718901508</v>
       </c>
       <c r="E191" t="n">
-        <v>444.19</v>
+        <v>436.515</v>
       </c>
       <c r="F191" t="n">
-        <v>165.8110091932211</v>
+        <v>168.726371770814</v>
       </c>
       <c r="G191" t="n">
-        <v>24963.23633673095</v>
+        <v>34923.36026574186</v>
       </c>
       <c r="H191" t="n">
-        <v>-7442.612669115069</v>
+        <v>-9360.308785346659</v>
       </c>
       <c r="I191" t="n">
-        <v>4.63</v>
+        <v>4.585</v>
       </c>
       <c r="J191" t="n">
-        <v>10.22</v>
+        <v>9.805</v>
       </c>
       <c r="K191" t="n">
-        <v>1.65</v>
+        <v>1.655</v>
       </c>
       <c r="L191" t="n">
-        <v>2.425</v>
+        <v>2.43</v>
       </c>
       <c r="M191" t="n">
-        <v>300.0729606139864</v>
+        <v>300.1745888736389</v>
       </c>
       <c r="N191" t="n">
-        <v>7.263482551286738</v>
+        <v>7.214413147291361</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="B192" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C192" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="D192" t="n">
-        <v>89.18663858636465</v>
+        <v>87.80320469212297</v>
       </c>
       <c r="E192" t="n">
-        <v>444.19</v>
+        <v>436.505</v>
       </c>
       <c r="F192" t="n">
-        <v>165.8110091932211</v>
+        <v>168.7302371646072</v>
       </c>
       <c r="G192" t="n">
-        <v>24963.23633673095</v>
+        <v>34925.44109556412</v>
       </c>
       <c r="H192" t="n">
-        <v>-7442.612669115069</v>
+        <v>-9359.421098322955</v>
       </c>
       <c r="I192" t="n">
-        <v>4.63</v>
+        <v>4.585</v>
       </c>
       <c r="J192" t="n">
-        <v>10.22</v>
+        <v>9.805</v>
       </c>
       <c r="K192" t="n">
-        <v>1.65</v>
+        <v>1.655</v>
       </c>
       <c r="L192" t="n">
-        <v>2.425</v>
+        <v>2.43</v>
       </c>
       <c r="M192" t="n">
-        <v>300.0729606139864</v>
+        <v>300.1745888736489</v>
       </c>
       <c r="N192" t="n">
-        <v>7.263482551286738</v>
+        <v>7.214413147291324</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="B193" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C193" t="n">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="D193" t="n">
-        <v>89.18663858636465</v>
+        <v>87.80383718901508</v>
       </c>
       <c r="E193" t="n">
-        <v>444.19</v>
+        <v>436.515</v>
       </c>
       <c r="F193" t="n">
-        <v>165.8110091932211</v>
+        <v>168.726371770814</v>
       </c>
       <c r="G193" t="n">
-        <v>24963.23633673095</v>
+        <v>34923.36026574186</v>
       </c>
       <c r="H193" t="n">
-        <v>-7442.612669115069</v>
+        <v>-9360.308785346659</v>
       </c>
       <c r="I193" t="n">
-        <v>4.63</v>
+        <v>4.585</v>
       </c>
       <c r="J193" t="n">
-        <v>10.22</v>
+        <v>9.805</v>
       </c>
       <c r="K193" t="n">
-        <v>1.65</v>
+        <v>1.655</v>
       </c>
       <c r="L193" t="n">
-        <v>2.425</v>
+        <v>2.43</v>
       </c>
       <c r="M193" t="n">
-        <v>300.0729606139864</v>
+        <v>300.1745888736389</v>
       </c>
       <c r="N193" t="n">
-        <v>7.263482551286738</v>
+        <v>7.214413147291361</v>
       </c>
     </row>
     <row r="194">
@@ -8953,7 +8953,7 @@
         <v>304</v>
       </c>
       <c r="B194" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C194" t="n">
         <v>304</v>
@@ -8997,7 +8997,7 @@
         <v>304</v>
       </c>
       <c r="B195" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C195" t="n">
         <v>304</v>
@@ -9041,7 +9041,7 @@
         <v>304</v>
       </c>
       <c r="B196" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C196" t="n">
         <v>304</v>
@@ -9085,7 +9085,7 @@
         <v>304</v>
       </c>
       <c r="B197" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C197" t="n">
         <v>304</v>
@@ -9129,43 +9129,43 @@
         <v>304</v>
       </c>
       <c r="B198" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C198" t="n">
         <v>304</v>
       </c>
       <c r="D198" t="n">
-        <v>88.92269833940205</v>
+        <v>89.18663858636465</v>
       </c>
       <c r="E198" t="n">
-        <v>443.335</v>
+        <v>444.19</v>
       </c>
       <c r="F198" t="n">
-        <v>166.1307863659239</v>
+        <v>165.8110091932211</v>
       </c>
       <c r="G198" t="n">
-        <v>25999.58864210363</v>
+        <v>24963.23633673095</v>
       </c>
       <c r="H198" t="n">
-        <v>-7725.87995802869</v>
+        <v>-7442.612669115069</v>
       </c>
       <c r="I198" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="J198" t="n">
-        <v>10.17</v>
+        <v>10.22</v>
       </c>
       <c r="K198" t="n">
-        <v>1.645</v>
+        <v>1.65</v>
       </c>
       <c r="L198" t="n">
-        <v>2.42</v>
+        <v>2.425</v>
       </c>
       <c r="M198" t="n">
-        <v>300.0729673247968</v>
+        <v>300.0729606139864</v>
       </c>
       <c r="N198" t="n">
-        <v>7.263515293189545</v>
+        <v>7.263482551286738</v>
       </c>
     </row>
     <row r="199">
@@ -9173,43 +9173,43 @@
         <v>304</v>
       </c>
       <c r="B199" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C199" t="n">
         <v>304</v>
       </c>
       <c r="D199" t="n">
-        <v>88.92269833940205</v>
+        <v>89.18663858636465</v>
       </c>
       <c r="E199" t="n">
-        <v>443.335</v>
+        <v>444.19</v>
       </c>
       <c r="F199" t="n">
-        <v>166.1307863659239</v>
+        <v>165.8110091932211</v>
       </c>
       <c r="G199" t="n">
-        <v>25999.58864210363</v>
+        <v>24963.23633673095</v>
       </c>
       <c r="H199" t="n">
-        <v>-7725.87995802869</v>
+        <v>-7442.612669115069</v>
       </c>
       <c r="I199" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="J199" t="n">
-        <v>10.17</v>
+        <v>10.22</v>
       </c>
       <c r="K199" t="n">
-        <v>1.645</v>
+        <v>1.65</v>
       </c>
       <c r="L199" t="n">
-        <v>2.42</v>
+        <v>2.425</v>
       </c>
       <c r="M199" t="n">
-        <v>300.0729673247968</v>
+        <v>300.0729606139864</v>
       </c>
       <c r="N199" t="n">
-        <v>7.263515293189545</v>
+        <v>7.263482551286738</v>
       </c>
     </row>
     <row r="200">
@@ -9217,43 +9217,43 @@
         <v>304</v>
       </c>
       <c r="B200" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C200" t="n">
         <v>304</v>
       </c>
       <c r="D200" t="n">
-        <v>88.92269833940205</v>
+        <v>89.18663858636465</v>
       </c>
       <c r="E200" t="n">
-        <v>443.335</v>
+        <v>444.19</v>
       </c>
       <c r="F200" t="n">
-        <v>166.1307863659239</v>
+        <v>165.8110091932211</v>
       </c>
       <c r="G200" t="n">
-        <v>25999.58864210363</v>
+        <v>24963.23633673095</v>
       </c>
       <c r="H200" t="n">
-        <v>-7725.87995802869</v>
+        <v>-7442.612669115069</v>
       </c>
       <c r="I200" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="J200" t="n">
-        <v>10.17</v>
+        <v>10.22</v>
       </c>
       <c r="K200" t="n">
-        <v>1.645</v>
+        <v>1.65</v>
       </c>
       <c r="L200" t="n">
-        <v>2.42</v>
+        <v>2.425</v>
       </c>
       <c r="M200" t="n">
-        <v>300.0729673247968</v>
+        <v>300.0729606139864</v>
       </c>
       <c r="N200" t="n">
-        <v>7.263515293189545</v>
+        <v>7.263482551286738</v>
       </c>
     </row>
     <row r="201">
@@ -9261,43 +9261,43 @@
         <v>304</v>
       </c>
       <c r="B201" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C201" t="n">
         <v>304</v>
       </c>
       <c r="D201" t="n">
-        <v>88.92269833940205</v>
+        <v>89.18663858636465</v>
       </c>
       <c r="E201" t="n">
-        <v>443.335</v>
+        <v>444.19</v>
       </c>
       <c r="F201" t="n">
-        <v>166.1307863659239</v>
+        <v>165.8110091932211</v>
       </c>
       <c r="G201" t="n">
-        <v>25999.58864210363</v>
+        <v>24963.23633673095</v>
       </c>
       <c r="H201" t="n">
-        <v>-7725.87995802869</v>
+        <v>-7442.612669115069</v>
       </c>
       <c r="I201" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="J201" t="n">
-        <v>10.17</v>
+        <v>10.22</v>
       </c>
       <c r="K201" t="n">
-        <v>1.645</v>
+        <v>1.65</v>
       </c>
       <c r="L201" t="n">
-        <v>2.42</v>
+        <v>2.425</v>
       </c>
       <c r="M201" t="n">
-        <v>300.0729673247968</v>
+        <v>300.0729606139864</v>
       </c>
       <c r="N201" t="n">
-        <v>7.263515293189545</v>
+        <v>7.263482551286738</v>
       </c>
     </row>
     <row r="202">
@@ -9305,7 +9305,7 @@
         <v>304</v>
       </c>
       <c r="B202" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C202" t="n">
         <v>304</v>
@@ -9349,7 +9349,7 @@
         <v>304</v>
       </c>
       <c r="B203" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C203" t="n">
         <v>304</v>
@@ -9393,7 +9393,7 @@
         <v>304</v>
       </c>
       <c r="B204" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C204" t="n">
         <v>304</v>
@@ -9437,7 +9437,7 @@
         <v>304</v>
       </c>
       <c r="B205" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C205" t="n">
         <v>304</v>
@@ -9481,31 +9481,31 @@
         <v>304</v>
       </c>
       <c r="B206" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C206" t="n">
         <v>304</v>
       </c>
       <c r="D206" t="n">
-        <v>88.64953363406018</v>
+        <v>88.92269833940205</v>
       </c>
       <c r="E206" t="n">
-        <v>441.785</v>
+        <v>443.335</v>
       </c>
       <c r="F206" t="n">
-        <v>166.71365522491</v>
+        <v>166.1307863659239</v>
       </c>
       <c r="G206" t="n">
-        <v>27096.49973564107</v>
+        <v>25999.58864210363</v>
       </c>
       <c r="H206" t="n">
-        <v>-8051.750862810792</v>
+        <v>-7725.87995802869</v>
       </c>
       <c r="I206" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="J206" t="n">
-        <v>10.175</v>
+        <v>10.17</v>
       </c>
       <c r="K206" t="n">
         <v>1.645</v>
@@ -9514,10 +9514,10 @@
         <v>2.42</v>
       </c>
       <c r="M206" t="n">
-        <v>300.072977811907</v>
+        <v>300.0729673247968</v>
       </c>
       <c r="N206" t="n">
-        <v>7.2635473494556</v>
+        <v>7.263515293189545</v>
       </c>
     </row>
     <row r="207">
@@ -9525,31 +9525,31 @@
         <v>304</v>
       </c>
       <c r="B207" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C207" t="n">
         <v>304</v>
       </c>
       <c r="D207" t="n">
-        <v>88.64953363406018</v>
+        <v>88.92269833940205</v>
       </c>
       <c r="E207" t="n">
-        <v>441.785</v>
+        <v>443.335</v>
       </c>
       <c r="F207" t="n">
-        <v>166.71365522491</v>
+        <v>166.1307863659239</v>
       </c>
       <c r="G207" t="n">
-        <v>27096.49973564107</v>
+        <v>25999.58864210363</v>
       </c>
       <c r="H207" t="n">
-        <v>-8051.750862810792</v>
+        <v>-7725.87995802869</v>
       </c>
       <c r="I207" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="J207" t="n">
-        <v>10.175</v>
+        <v>10.17</v>
       </c>
       <c r="K207" t="n">
         <v>1.645</v>
@@ -9558,10 +9558,10 @@
         <v>2.42</v>
       </c>
       <c r="M207" t="n">
-        <v>300.072977811907</v>
+        <v>300.0729673247968</v>
       </c>
       <c r="N207" t="n">
-        <v>7.2635473494556</v>
+        <v>7.263515293189545</v>
       </c>
     </row>
     <row r="208">
@@ -9569,31 +9569,31 @@
         <v>304</v>
       </c>
       <c r="B208" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C208" t="n">
         <v>304</v>
       </c>
       <c r="D208" t="n">
-        <v>88.64953363406018</v>
+        <v>88.92269833940205</v>
       </c>
       <c r="E208" t="n">
-        <v>441.785</v>
+        <v>443.335</v>
       </c>
       <c r="F208" t="n">
-        <v>166.71365522491</v>
+        <v>166.1307863659239</v>
       </c>
       <c r="G208" t="n">
-        <v>27096.49973564107</v>
+        <v>25999.58864210363</v>
       </c>
       <c r="H208" t="n">
-        <v>-8051.750862810792</v>
+        <v>-7725.87995802869</v>
       </c>
       <c r="I208" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="J208" t="n">
-        <v>10.175</v>
+        <v>10.17</v>
       </c>
       <c r="K208" t="n">
         <v>1.645</v>
@@ -9602,10 +9602,10 @@
         <v>2.42</v>
       </c>
       <c r="M208" t="n">
-        <v>300.072977811907</v>
+        <v>300.0729673247968</v>
       </c>
       <c r="N208" t="n">
-        <v>7.2635473494556</v>
+        <v>7.263515293189545</v>
       </c>
     </row>
     <row r="209">
@@ -9613,31 +9613,31 @@
         <v>304</v>
       </c>
       <c r="B209" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C209" t="n">
         <v>304</v>
       </c>
       <c r="D209" t="n">
-        <v>88.64953363406018</v>
+        <v>88.92269833940205</v>
       </c>
       <c r="E209" t="n">
-        <v>441.785</v>
+        <v>443.335</v>
       </c>
       <c r="F209" t="n">
-        <v>166.71365522491</v>
+        <v>166.1307863659239</v>
       </c>
       <c r="G209" t="n">
-        <v>27096.49973564107</v>
+        <v>25999.58864210363</v>
       </c>
       <c r="H209" t="n">
-        <v>-8051.750862810792</v>
+        <v>-7725.87995802869</v>
       </c>
       <c r="I209" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="J209" t="n">
-        <v>10.175</v>
+        <v>10.17</v>
       </c>
       <c r="K209" t="n">
         <v>1.645</v>
@@ -9646,10 +9646,10 @@
         <v>2.42</v>
       </c>
       <c r="M209" t="n">
-        <v>300.072977811907</v>
+        <v>300.0729673247968</v>
       </c>
       <c r="N209" t="n">
-        <v>7.2635473494556</v>
+        <v>7.263515293189545</v>
       </c>
     </row>
     <row r="210">
@@ -9657,7 +9657,7 @@
         <v>304</v>
       </c>
       <c r="B210" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C210" t="n">
         <v>304</v>
@@ -9701,7 +9701,7 @@
         <v>304</v>
       </c>
       <c r="B211" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C211" t="n">
         <v>304</v>
@@ -9745,7 +9745,7 @@
         <v>304</v>
       </c>
       <c r="B212" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C212" t="n">
         <v>304</v>
@@ -9789,7 +9789,7 @@
         <v>304</v>
       </c>
       <c r="B213" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C213" t="n">
         <v>304</v>
@@ -9833,43 +9833,43 @@
         <v>304</v>
       </c>
       <c r="B214" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C214" t="n">
         <v>304</v>
       </c>
       <c r="D214" t="n">
-        <v>88.34768801973219</v>
+        <v>88.64953363406018</v>
       </c>
       <c r="E214" t="n">
-        <v>441.42</v>
+        <v>441.785</v>
       </c>
       <c r="F214" t="n">
-        <v>166.8515068948776</v>
+        <v>166.71365522491</v>
       </c>
       <c r="G214" t="n">
-        <v>28207.75879230446</v>
+        <v>27096.49973564107</v>
       </c>
       <c r="H214" t="n">
-        <v>-8301.890591027455</v>
+        <v>-8051.750862810792</v>
       </c>
       <c r="I214" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="J214" t="n">
-        <v>10.195</v>
+        <v>10.175</v>
       </c>
       <c r="K214" t="n">
-        <v>1.64</v>
+        <v>1.645</v>
       </c>
       <c r="L214" t="n">
-        <v>2.415</v>
+        <v>2.42</v>
       </c>
       <c r="M214" t="n">
-        <v>300.0729467134203</v>
+        <v>300.072977811907</v>
       </c>
       <c r="N214" t="n">
-        <v>7.263577527694797</v>
+        <v>7.2635473494556</v>
       </c>
     </row>
     <row r="215">
@@ -9877,43 +9877,43 @@
         <v>304</v>
       </c>
       <c r="B215" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C215" t="n">
         <v>304</v>
       </c>
       <c r="D215" t="n">
-        <v>88.34768801973219</v>
+        <v>88.64953363406018</v>
       </c>
       <c r="E215" t="n">
-        <v>441.42</v>
+        <v>441.785</v>
       </c>
       <c r="F215" t="n">
-        <v>166.8515068948776</v>
+        <v>166.71365522491</v>
       </c>
       <c r="G215" t="n">
-        <v>28207.75879230446</v>
+        <v>27096.49973564107</v>
       </c>
       <c r="H215" t="n">
-        <v>-8301.890591027455</v>
+        <v>-8051.750862810792</v>
       </c>
       <c r="I215" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="J215" t="n">
-        <v>10.195</v>
+        <v>10.175</v>
       </c>
       <c r="K215" t="n">
-        <v>1.64</v>
+        <v>1.645</v>
       </c>
       <c r="L215" t="n">
-        <v>2.415</v>
+        <v>2.42</v>
       </c>
       <c r="M215" t="n">
-        <v>300.0729467134203</v>
+        <v>300.072977811907</v>
       </c>
       <c r="N215" t="n">
-        <v>7.263577527694797</v>
+        <v>7.2635473494556</v>
       </c>
     </row>
     <row r="216">
@@ -9921,43 +9921,43 @@
         <v>304</v>
       </c>
       <c r="B216" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C216" t="n">
         <v>304</v>
       </c>
       <c r="D216" t="n">
-        <v>88.34768801973219</v>
+        <v>88.64953363406018</v>
       </c>
       <c r="E216" t="n">
-        <v>441.42</v>
+        <v>441.785</v>
       </c>
       <c r="F216" t="n">
-        <v>166.8515068948776</v>
+        <v>166.71365522491</v>
       </c>
       <c r="G216" t="n">
-        <v>28207.75879230446</v>
+        <v>27096.49973564107</v>
       </c>
       <c r="H216" t="n">
-        <v>-8301.890591027455</v>
+        <v>-8051.750862810792</v>
       </c>
       <c r="I216" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="J216" t="n">
-        <v>10.195</v>
+        <v>10.175</v>
       </c>
       <c r="K216" t="n">
-        <v>1.64</v>
+        <v>1.645</v>
       </c>
       <c r="L216" t="n">
-        <v>2.415</v>
+        <v>2.42</v>
       </c>
       <c r="M216" t="n">
-        <v>300.0729467134203</v>
+        <v>300.072977811907</v>
       </c>
       <c r="N216" t="n">
-        <v>7.263577527694797</v>
+        <v>7.2635473494556</v>
       </c>
     </row>
     <row r="217">
@@ -9965,43 +9965,43 @@
         <v>304</v>
       </c>
       <c r="B217" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C217" t="n">
         <v>304</v>
       </c>
       <c r="D217" t="n">
-        <v>88.34768801973219</v>
+        <v>88.64953363406018</v>
       </c>
       <c r="E217" t="n">
-        <v>441.42</v>
+        <v>441.785</v>
       </c>
       <c r="F217" t="n">
-        <v>166.8515068948776</v>
+        <v>166.71365522491</v>
       </c>
       <c r="G217" t="n">
-        <v>28207.75879230446</v>
+        <v>27096.49973564107</v>
       </c>
       <c r="H217" t="n">
-        <v>-8301.890591027455</v>
+        <v>-8051.750862810792</v>
       </c>
       <c r="I217" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="J217" t="n">
-        <v>10.195</v>
+        <v>10.175</v>
       </c>
       <c r="K217" t="n">
-        <v>1.64</v>
+        <v>1.645</v>
       </c>
       <c r="L217" t="n">
-        <v>2.415</v>
+        <v>2.42</v>
       </c>
       <c r="M217" t="n">
-        <v>300.0729467134203</v>
+        <v>300.072977811907</v>
       </c>
       <c r="N217" t="n">
-        <v>7.263577527694797</v>
+        <v>7.2635473494556</v>
       </c>
     </row>
     <row r="218">
@@ -10009,7 +10009,7 @@
         <v>304</v>
       </c>
       <c r="B218" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C218" t="n">
         <v>304</v>
@@ -10053,7 +10053,7 @@
         <v>304</v>
       </c>
       <c r="B219" t="n">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C219" t="n">
         <v>304</v>
@@ -10097,7 +10097,7 @@
         <v>304</v>
       </c>
       <c r="B220" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C220" t="n">
         <v>304</v>
@@ -10141,7 +10141,7 @@
         <v>304</v>
       </c>
       <c r="B221" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C221" t="n">
         <v>304</v>
@@ -10182,178 +10182,178 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B222" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C222" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D222" t="n">
-        <v>93.51628632039747</v>
+        <v>88.34768801973219</v>
       </c>
       <c r="E222" t="n">
-        <v>480.2</v>
+        <v>441.42</v>
       </c>
       <c r="F222" t="n">
-        <v>153.3769099823758</v>
+        <v>166.8515068948776</v>
       </c>
       <c r="G222" t="n">
-        <v>6124.376148017551</v>
+        <v>28207.75879230446</v>
       </c>
       <c r="H222" t="n">
-        <v>-1470.545677185506</v>
+        <v>-8301.890591027455</v>
       </c>
       <c r="I222" t="n">
-        <v>5.78</v>
+        <v>4.69</v>
       </c>
       <c r="J222" t="n">
-        <v>16.915</v>
+        <v>10.195</v>
       </c>
       <c r="K222" t="n">
-        <v>2.575</v>
+        <v>1.64</v>
       </c>
       <c r="L222" t="n">
-        <v>3.655</v>
+        <v>2.415</v>
       </c>
       <c r="M222" t="n">
-        <v>264.0036818737114</v>
+        <v>300.0729467134203</v>
       </c>
       <c r="N222" t="n">
-        <v>5.252724587563517</v>
+        <v>7.263577527694797</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B223" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C223" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D223" t="n">
-        <v>93.51628632039747</v>
+        <v>88.34768801973219</v>
       </c>
       <c r="E223" t="n">
-        <v>480.2</v>
+        <v>441.42</v>
       </c>
       <c r="F223" t="n">
-        <v>153.3769099823758</v>
+        <v>166.8515068948776</v>
       </c>
       <c r="G223" t="n">
-        <v>6124.376148017551</v>
+        <v>28207.75879230446</v>
       </c>
       <c r="H223" t="n">
-        <v>-1470.545677185506</v>
+        <v>-8301.890591027455</v>
       </c>
       <c r="I223" t="n">
-        <v>5.78</v>
+        <v>4.69</v>
       </c>
       <c r="J223" t="n">
-        <v>16.915</v>
+        <v>10.195</v>
       </c>
       <c r="K223" t="n">
-        <v>2.575</v>
+        <v>1.64</v>
       </c>
       <c r="L223" t="n">
-        <v>3.655</v>
+        <v>2.415</v>
       </c>
       <c r="M223" t="n">
-        <v>264.0036818737114</v>
+        <v>300.0729467134203</v>
       </c>
       <c r="N223" t="n">
-        <v>5.252724587563517</v>
+        <v>7.263577527694797</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B224" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C224" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D224" t="n">
-        <v>93.51628632039747</v>
+        <v>88.34768801973219</v>
       </c>
       <c r="E224" t="n">
-        <v>480.2</v>
+        <v>441.42</v>
       </c>
       <c r="F224" t="n">
-        <v>153.3769099823758</v>
+        <v>166.8515068948776</v>
       </c>
       <c r="G224" t="n">
-        <v>6124.376148017551</v>
+        <v>28207.75879230446</v>
       </c>
       <c r="H224" t="n">
-        <v>-1470.545677185506</v>
+        <v>-8301.890591027455</v>
       </c>
       <c r="I224" t="n">
-        <v>5.78</v>
+        <v>4.69</v>
       </c>
       <c r="J224" t="n">
-        <v>16.915</v>
+        <v>10.195</v>
       </c>
       <c r="K224" t="n">
-        <v>2.575</v>
+        <v>1.64</v>
       </c>
       <c r="L224" t="n">
-        <v>3.655</v>
+        <v>2.415</v>
       </c>
       <c r="M224" t="n">
-        <v>264.0036818737114</v>
+        <v>300.0729467134203</v>
       </c>
       <c r="N224" t="n">
-        <v>5.252724587563517</v>
+        <v>7.263577527694797</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B225" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C225" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D225" t="n">
-        <v>93.51628632039747</v>
+        <v>88.34768801973219</v>
       </c>
       <c r="E225" t="n">
-        <v>480.2</v>
+        <v>441.42</v>
       </c>
       <c r="F225" t="n">
-        <v>153.3769099823758</v>
+        <v>166.8515068948776</v>
       </c>
       <c r="G225" t="n">
-        <v>6124.376148017551</v>
+        <v>28207.75879230446</v>
       </c>
       <c r="H225" t="n">
-        <v>-1470.545677185506</v>
+        <v>-8301.890591027455</v>
       </c>
       <c r="I225" t="n">
-        <v>5.78</v>
+        <v>4.69</v>
       </c>
       <c r="J225" t="n">
-        <v>16.915</v>
+        <v>10.195</v>
       </c>
       <c r="K225" t="n">
-        <v>2.575</v>
+        <v>1.64</v>
       </c>
       <c r="L225" t="n">
-        <v>3.655</v>
+        <v>2.415</v>
       </c>
       <c r="M225" t="n">
-        <v>264.0036818737114</v>
+        <v>300.0729467134203</v>
       </c>
       <c r="N225" t="n">
-        <v>5.252724587563517</v>
+        <v>7.263577527694797</v>
       </c>
     </row>
     <row r="226">
@@ -10361,7 +10361,7 @@
         <v>317</v>
       </c>
       <c r="B226" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C226" t="n">
         <v>317</v>
@@ -10405,7 +10405,7 @@
         <v>317</v>
       </c>
       <c r="B227" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C227" t="n">
         <v>317</v>
@@ -10449,7 +10449,7 @@
         <v>317</v>
       </c>
       <c r="B228" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C228" t="n">
         <v>317</v>
@@ -10493,7 +10493,7 @@
         <v>317</v>
       </c>
       <c r="B229" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C229" t="n">
         <v>317</v>
@@ -10537,43 +10537,43 @@
         <v>317</v>
       </c>
       <c r="B230" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C230" t="n">
         <v>317</v>
       </c>
       <c r="D230" t="n">
-        <v>93.48138565448045</v>
+        <v>93.51628632039747</v>
       </c>
       <c r="E230" t="n">
-        <v>476.185</v>
+        <v>480.2</v>
       </c>
       <c r="F230" t="n">
-        <v>154.6701222708336</v>
+        <v>153.3769099823758</v>
       </c>
       <c r="G230" t="n">
-        <v>6333.855935097919</v>
+        <v>6124.376148017551</v>
       </c>
       <c r="H230" t="n">
-        <v>-1573.306435878632</v>
+        <v>-1470.545677185506</v>
       </c>
       <c r="I230" t="n">
-        <v>5.765</v>
+        <v>5.78</v>
       </c>
       <c r="J230" t="n">
-        <v>16.195</v>
+        <v>16.915</v>
       </c>
       <c r="K230" t="n">
-        <v>2.48</v>
+        <v>2.575</v>
       </c>
       <c r="L230" t="n">
-        <v>3.56</v>
+        <v>3.655</v>
       </c>
       <c r="M230" t="n">
-        <v>264.0313823695389</v>
+        <v>264.0036818737114</v>
       </c>
       <c r="N230" t="n">
-        <v>5.252746615891848</v>
+        <v>5.252724587563517</v>
       </c>
     </row>
     <row r="231">
@@ -10581,43 +10581,43 @@
         <v>317</v>
       </c>
       <c r="B231" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C231" t="n">
         <v>317</v>
       </c>
       <c r="D231" t="n">
-        <v>93.48138565448045</v>
+        <v>93.51628632039747</v>
       </c>
       <c r="E231" t="n">
-        <v>476.185</v>
+        <v>480.2</v>
       </c>
       <c r="F231" t="n">
-        <v>154.6701222708336</v>
+        <v>153.3769099823758</v>
       </c>
       <c r="G231" t="n">
-        <v>6333.855935097919</v>
+        <v>6124.376148017551</v>
       </c>
       <c r="H231" t="n">
-        <v>-1573.306435878632</v>
+        <v>-1470.545677185506</v>
       </c>
       <c r="I231" t="n">
-        <v>5.765</v>
+        <v>5.78</v>
       </c>
       <c r="J231" t="n">
-        <v>16.195</v>
+        <v>16.915</v>
       </c>
       <c r="K231" t="n">
-        <v>2.48</v>
+        <v>2.575</v>
       </c>
       <c r="L231" t="n">
-        <v>3.56</v>
+        <v>3.655</v>
       </c>
       <c r="M231" t="n">
-        <v>264.0313823695389</v>
+        <v>264.0036818737114</v>
       </c>
       <c r="N231" t="n">
-        <v>5.252746615891848</v>
+        <v>5.252724587563517</v>
       </c>
     </row>
     <row r="232">
@@ -10625,43 +10625,43 @@
         <v>317</v>
       </c>
       <c r="B232" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C232" t="n">
         <v>317</v>
       </c>
       <c r="D232" t="n">
-        <v>93.48138565448045</v>
+        <v>93.51628632039747</v>
       </c>
       <c r="E232" t="n">
-        <v>476.185</v>
+        <v>480.2</v>
       </c>
       <c r="F232" t="n">
-        <v>154.6701222708336</v>
+        <v>153.3769099823758</v>
       </c>
       <c r="G232" t="n">
-        <v>6333.855935097919</v>
+        <v>6124.376148017551</v>
       </c>
       <c r="H232" t="n">
-        <v>-1573.306435878632</v>
+        <v>-1470.545677185506</v>
       </c>
       <c r="I232" t="n">
-        <v>5.765</v>
+        <v>5.78</v>
       </c>
       <c r="J232" t="n">
-        <v>16.195</v>
+        <v>16.915</v>
       </c>
       <c r="K232" t="n">
-        <v>2.48</v>
+        <v>2.575</v>
       </c>
       <c r="L232" t="n">
-        <v>3.56</v>
+        <v>3.655</v>
       </c>
       <c r="M232" t="n">
-        <v>264.0313823695389</v>
+        <v>264.0036818737114</v>
       </c>
       <c r="N232" t="n">
-        <v>5.252746615891848</v>
+        <v>5.252724587563517</v>
       </c>
     </row>
     <row r="233">
@@ -10669,43 +10669,43 @@
         <v>317</v>
       </c>
       <c r="B233" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C233" t="n">
         <v>317</v>
       </c>
       <c r="D233" t="n">
-        <v>93.48138565448045</v>
+        <v>93.51628632039747</v>
       </c>
       <c r="E233" t="n">
-        <v>476.185</v>
+        <v>480.2</v>
       </c>
       <c r="F233" t="n">
-        <v>154.6701222708336</v>
+        <v>153.3769099823758</v>
       </c>
       <c r="G233" t="n">
-        <v>6333.855935097919</v>
+        <v>6124.376148017551</v>
       </c>
       <c r="H233" t="n">
-        <v>-1573.306435878632</v>
+        <v>-1470.545677185506</v>
       </c>
       <c r="I233" t="n">
-        <v>5.765</v>
+        <v>5.78</v>
       </c>
       <c r="J233" t="n">
-        <v>16.195</v>
+        <v>16.915</v>
       </c>
       <c r="K233" t="n">
-        <v>2.48</v>
+        <v>2.575</v>
       </c>
       <c r="L233" t="n">
-        <v>3.56</v>
+        <v>3.655</v>
       </c>
       <c r="M233" t="n">
-        <v>264.0313823695389</v>
+        <v>264.0036818737114</v>
       </c>
       <c r="N233" t="n">
-        <v>5.252746615891848</v>
+        <v>5.252724587563517</v>
       </c>
     </row>
     <row r="234">
@@ -10713,7 +10713,7 @@
         <v>317</v>
       </c>
       <c r="B234" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C234" t="n">
         <v>317</v>
@@ -10757,7 +10757,7 @@
         <v>317</v>
       </c>
       <c r="B235" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C235" t="n">
         <v>317</v>
@@ -10801,7 +10801,7 @@
         <v>317</v>
       </c>
       <c r="B236" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C236" t="n">
         <v>317</v>
@@ -10845,7 +10845,7 @@
         <v>317</v>
       </c>
       <c r="B237" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C237" t="n">
         <v>317</v>
@@ -10889,43 +10889,43 @@
         <v>317</v>
       </c>
       <c r="B238" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C238" t="n">
         <v>317</v>
       </c>
       <c r="D238" t="n">
-        <v>93.43772805869679</v>
+        <v>93.48138565448045</v>
       </c>
       <c r="E238" t="n">
-        <v>473.98</v>
+        <v>476.185</v>
       </c>
       <c r="F238" t="n">
-        <v>155.3896623771823</v>
+        <v>154.6701222708336</v>
       </c>
       <c r="G238" t="n">
-        <v>6570.05734754422</v>
+        <v>6333.855935097919</v>
       </c>
       <c r="H238" t="n">
-        <v>-1675.458575039167</v>
+        <v>-1573.306435878632</v>
       </c>
       <c r="I238" t="n">
-        <v>5.77</v>
+        <v>5.765</v>
       </c>
       <c r="J238" t="n">
-        <v>15.61</v>
+        <v>16.195</v>
       </c>
       <c r="K238" t="n">
-        <v>2.425</v>
+        <v>2.48</v>
       </c>
       <c r="L238" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="M238" t="n">
-        <v>264.0598199087914</v>
+        <v>264.0313823695389</v>
       </c>
       <c r="N238" t="n">
-        <v>5.252767184544403</v>
+        <v>5.252746615891848</v>
       </c>
     </row>
     <row r="239">
@@ -10933,43 +10933,43 @@
         <v>317</v>
       </c>
       <c r="B239" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C239" t="n">
         <v>317</v>
       </c>
       <c r="D239" t="n">
-        <v>93.43772805869679</v>
+        <v>93.48138565448045</v>
       </c>
       <c r="E239" t="n">
-        <v>473.98</v>
+        <v>476.185</v>
       </c>
       <c r="F239" t="n">
-        <v>155.3896623771823</v>
+        <v>154.6701222708336</v>
       </c>
       <c r="G239" t="n">
-        <v>6570.05734754422</v>
+        <v>6333.855935097919</v>
       </c>
       <c r="H239" t="n">
-        <v>-1675.458575039167</v>
+        <v>-1573.306435878632</v>
       </c>
       <c r="I239" t="n">
-        <v>5.77</v>
+        <v>5.765</v>
       </c>
       <c r="J239" t="n">
-        <v>15.61</v>
+        <v>16.195</v>
       </c>
       <c r="K239" t="n">
-        <v>2.425</v>
+        <v>2.48</v>
       </c>
       <c r="L239" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="M239" t="n">
-        <v>264.0598199087914</v>
+        <v>264.0313823695389</v>
       </c>
       <c r="N239" t="n">
-        <v>5.252767184544403</v>
+        <v>5.252746615891848</v>
       </c>
     </row>
     <row r="240">
@@ -10977,43 +10977,43 @@
         <v>317</v>
       </c>
       <c r="B240" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C240" t="n">
         <v>317</v>
       </c>
       <c r="D240" t="n">
-        <v>93.43772805869679</v>
+        <v>93.48138565448045</v>
       </c>
       <c r="E240" t="n">
-        <v>473.98</v>
+        <v>476.185</v>
       </c>
       <c r="F240" t="n">
-        <v>155.3896623771823</v>
+        <v>154.6701222708336</v>
       </c>
       <c r="G240" t="n">
-        <v>6570.05734754422</v>
+        <v>6333.855935097919</v>
       </c>
       <c r="H240" t="n">
-        <v>-1675.458575039167</v>
+        <v>-1573.306435878632</v>
       </c>
       <c r="I240" t="n">
-        <v>5.77</v>
+        <v>5.765</v>
       </c>
       <c r="J240" t="n">
-        <v>15.61</v>
+        <v>16.195</v>
       </c>
       <c r="K240" t="n">
-        <v>2.425</v>
+        <v>2.48</v>
       </c>
       <c r="L240" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="M240" t="n">
-        <v>264.0598199087914</v>
+        <v>264.0313823695389</v>
       </c>
       <c r="N240" t="n">
-        <v>5.252767184544403</v>
+        <v>5.252746615891848</v>
       </c>
     </row>
     <row r="241">
@@ -11021,43 +11021,43 @@
         <v>317</v>
       </c>
       <c r="B241" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C241" t="n">
         <v>317</v>
       </c>
       <c r="D241" t="n">
-        <v>93.43772805869679</v>
+        <v>93.48138565448045</v>
       </c>
       <c r="E241" t="n">
-        <v>473.98</v>
+        <v>476.185</v>
       </c>
       <c r="F241" t="n">
-        <v>155.3896623771823</v>
+        <v>154.6701222708336</v>
       </c>
       <c r="G241" t="n">
-        <v>6570.05734754422</v>
+        <v>6333.855935097919</v>
       </c>
       <c r="H241" t="n">
-        <v>-1675.458575039167</v>
+        <v>-1573.306435878632</v>
       </c>
       <c r="I241" t="n">
-        <v>5.77</v>
+        <v>5.765</v>
       </c>
       <c r="J241" t="n">
-        <v>15.61</v>
+        <v>16.195</v>
       </c>
       <c r="K241" t="n">
-        <v>2.425</v>
+        <v>2.48</v>
       </c>
       <c r="L241" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="M241" t="n">
-        <v>264.0598199087914</v>
+        <v>264.0313823695389</v>
       </c>
       <c r="N241" t="n">
-        <v>5.252767184544403</v>
+        <v>5.252746615891848</v>
       </c>
     </row>
     <row r="242">
@@ -11065,7 +11065,7 @@
         <v>317</v>
       </c>
       <c r="B242" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C242" t="n">
         <v>317</v>
@@ -11109,7 +11109,7 @@
         <v>317</v>
       </c>
       <c r="B243" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C243" t="n">
         <v>317</v>
@@ -11153,7 +11153,7 @@
         <v>317</v>
       </c>
       <c r="B244" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C244" t="n">
         <v>317</v>
@@ -11197,7 +11197,7 @@
         <v>317</v>
       </c>
       <c r="B245" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C245" t="n">
         <v>317</v>
@@ -11241,43 +11241,43 @@
         <v>317</v>
       </c>
       <c r="B246" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C246" t="n">
         <v>317</v>
       </c>
       <c r="D246" t="n">
-        <v>93.41234092860827</v>
+        <v>93.43772805869679</v>
       </c>
       <c r="E246" t="n">
-        <v>471.15</v>
+        <v>473.98</v>
       </c>
       <c r="F246" t="n">
-        <v>156.3230227603457</v>
+        <v>155.3896623771823</v>
       </c>
       <c r="G246" t="n">
-        <v>6768.626139458149</v>
+        <v>6570.05734754422</v>
       </c>
       <c r="H246" t="n">
-        <v>-1797.684294448047</v>
+        <v>-1675.458575039167</v>
       </c>
       <c r="I246" t="n">
-        <v>5.785</v>
+        <v>5.77</v>
       </c>
       <c r="J246" t="n">
-        <v>15.115</v>
+        <v>15.61</v>
       </c>
       <c r="K246" t="n">
-        <v>2.390000000000001</v>
+        <v>2.425</v>
       </c>
       <c r="L246" t="n">
-        <v>3.465</v>
+        <v>3.5</v>
       </c>
       <c r="M246" t="n">
-        <v>264.0982794604473</v>
+        <v>264.0598199087914</v>
       </c>
       <c r="N246" t="n">
-        <v>5.252787017481772</v>
+        <v>5.252767184544403</v>
       </c>
     </row>
     <row r="247">
@@ -11285,43 +11285,43 @@
         <v>317</v>
       </c>
       <c r="B247" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C247" t="n">
         <v>317</v>
       </c>
       <c r="D247" t="n">
-        <v>93.41234092860827</v>
+        <v>93.43772805869679</v>
       </c>
       <c r="E247" t="n">
-        <v>471.15</v>
+        <v>473.98</v>
       </c>
       <c r="F247" t="n">
-        <v>156.3230227603457</v>
+        <v>155.3896623771823</v>
       </c>
       <c r="G247" t="n">
-        <v>6768.626139458149</v>
+        <v>6570.05734754422</v>
       </c>
       <c r="H247" t="n">
-        <v>-1797.684294448047</v>
+        <v>-1675.458575039167</v>
       </c>
       <c r="I247" t="n">
-        <v>5.785</v>
+        <v>5.77</v>
       </c>
       <c r="J247" t="n">
-        <v>15.115</v>
+        <v>15.61</v>
       </c>
       <c r="K247" t="n">
-        <v>2.390000000000001</v>
+        <v>2.425</v>
       </c>
       <c r="L247" t="n">
-        <v>3.465</v>
+        <v>3.5</v>
       </c>
       <c r="M247" t="n">
-        <v>264.0982794604473</v>
+        <v>264.0598199087914</v>
       </c>
       <c r="N247" t="n">
-        <v>5.252787017481772</v>
+        <v>5.252767184544403</v>
       </c>
     </row>
     <row r="248">
@@ -11329,43 +11329,43 @@
         <v>317</v>
       </c>
       <c r="B248" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C248" t="n">
         <v>317</v>
       </c>
       <c r="D248" t="n">
-        <v>93.41234092860827</v>
+        <v>93.43772805869679</v>
       </c>
       <c r="E248" t="n">
-        <v>471.15</v>
+        <v>473.98</v>
       </c>
       <c r="F248" t="n">
-        <v>156.3230227603457</v>
+        <v>155.3896623771823</v>
       </c>
       <c r="G248" t="n">
-        <v>6768.626139458149</v>
+        <v>6570.05734754422</v>
       </c>
       <c r="H248" t="n">
-        <v>-1797.684294448047</v>
+        <v>-1675.458575039167</v>
       </c>
       <c r="I248" t="n">
-        <v>5.785</v>
+        <v>5.77</v>
       </c>
       <c r="J248" t="n">
-        <v>15.115</v>
+        <v>15.61</v>
       </c>
       <c r="K248" t="n">
-        <v>2.390000000000001</v>
+        <v>2.425</v>
       </c>
       <c r="L248" t="n">
-        <v>3.465</v>
+        <v>3.5</v>
       </c>
       <c r="M248" t="n">
-        <v>264.0982794604473</v>
+        <v>264.0598199087914</v>
       </c>
       <c r="N248" t="n">
-        <v>5.252787017481772</v>
+        <v>5.252767184544403</v>
       </c>
     </row>
     <row r="249">
@@ -11373,43 +11373,43 @@
         <v>317</v>
       </c>
       <c r="B249" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C249" t="n">
         <v>317</v>
       </c>
       <c r="D249" t="n">
-        <v>93.41234092860827</v>
+        <v>93.43772805869679</v>
       </c>
       <c r="E249" t="n">
-        <v>471.15</v>
+        <v>473.98</v>
       </c>
       <c r="F249" t="n">
-        <v>156.3230227603457</v>
+        <v>155.3896623771823</v>
       </c>
       <c r="G249" t="n">
-        <v>6768.626139458149</v>
+        <v>6570.05734754422</v>
       </c>
       <c r="H249" t="n">
-        <v>-1797.684294448047</v>
+        <v>-1675.458575039167</v>
       </c>
       <c r="I249" t="n">
-        <v>5.785</v>
+        <v>5.77</v>
       </c>
       <c r="J249" t="n">
-        <v>15.115</v>
+        <v>15.61</v>
       </c>
       <c r="K249" t="n">
-        <v>2.390000000000001</v>
+        <v>2.425</v>
       </c>
       <c r="L249" t="n">
-        <v>3.465</v>
+        <v>3.5</v>
       </c>
       <c r="M249" t="n">
-        <v>264.0982794604473</v>
+        <v>264.0598199087914</v>
       </c>
       <c r="N249" t="n">
-        <v>5.252787017481772</v>
+        <v>5.252767184544403</v>
       </c>
     </row>
     <row r="250">
@@ -11417,7 +11417,7 @@
         <v>317</v>
       </c>
       <c r="B250" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C250" t="n">
         <v>317</v>
@@ -11461,7 +11461,7 @@
         <v>317</v>
       </c>
       <c r="B251" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C251" t="n">
         <v>317</v>
@@ -11505,7 +11505,7 @@
         <v>317</v>
       </c>
       <c r="B252" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C252" t="n">
         <v>317</v>
@@ -11549,7 +11549,7 @@
         <v>317</v>
       </c>
       <c r="B253" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C253" t="n">
         <v>317</v>
@@ -11590,178 +11590,178 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="B254" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C254" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="D254" t="n">
-        <v>81.10576822897893</v>
+        <v>93.41234092860827</v>
       </c>
       <c r="E254" t="n">
-        <v>465.35</v>
+        <v>471.15</v>
       </c>
       <c r="F254" t="n">
-        <v>158.2713917987254</v>
+        <v>156.3230227603457</v>
       </c>
       <c r="G254" t="n">
-        <v>53456.40773834212</v>
+        <v>6768.626139458149</v>
       </c>
       <c r="H254" t="n">
-        <v>-8709.7611760448</v>
+        <v>-1797.684294448047</v>
       </c>
       <c r="I254" t="n">
-        <v>5.76</v>
+        <v>5.785</v>
       </c>
       <c r="J254" t="n">
-        <v>15.18</v>
+        <v>15.115</v>
       </c>
       <c r="K254" t="n">
-        <v>2.365</v>
+        <v>2.390000000000001</v>
       </c>
       <c r="L254" t="n">
-        <v>3.395</v>
+        <v>3.465</v>
       </c>
       <c r="M254" t="n">
-        <v>300.0145777692024</v>
+        <v>264.0982794604473</v>
       </c>
       <c r="N254" t="n">
-        <v>5.445362991302629</v>
+        <v>5.252787017481772</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="B255" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C255" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="D255" t="n">
-        <v>81.1057682329695</v>
+        <v>93.41234092860827</v>
       </c>
       <c r="E255" t="n">
-        <v>465.35</v>
+        <v>471.15</v>
       </c>
       <c r="F255" t="n">
-        <v>158.2713917987254</v>
+        <v>156.3230227603457</v>
       </c>
       <c r="G255" t="n">
-        <v>53456.40773859157</v>
+        <v>6768.626139458149</v>
       </c>
       <c r="H255" t="n">
-        <v>-8709.761175251018</v>
+        <v>-1797.684294448047</v>
       </c>
       <c r="I255" t="n">
-        <v>5.76</v>
+        <v>5.785</v>
       </c>
       <c r="J255" t="n">
-        <v>15.18</v>
+        <v>15.115</v>
       </c>
       <c r="K255" t="n">
-        <v>2.365</v>
+        <v>2.390000000000001</v>
       </c>
       <c r="L255" t="n">
-        <v>3.395</v>
+        <v>3.465</v>
       </c>
       <c r="M255" t="n">
-        <v>300.0145777691984</v>
+        <v>264.0982794604473</v>
       </c>
       <c r="N255" t="n">
-        <v>5.445362991302568</v>
+        <v>5.252787017481772</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="B256" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C256" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="D256" t="n">
-        <v>81.10576822897893</v>
+        <v>93.41234092860827</v>
       </c>
       <c r="E256" t="n">
-        <v>465.35</v>
+        <v>471.15</v>
       </c>
       <c r="F256" t="n">
-        <v>158.2713917987254</v>
+        <v>156.3230227603457</v>
       </c>
       <c r="G256" t="n">
-        <v>53456.40773834212</v>
+        <v>6768.626139458149</v>
       </c>
       <c r="H256" t="n">
-        <v>-8709.7611760448</v>
+        <v>-1797.684294448047</v>
       </c>
       <c r="I256" t="n">
-        <v>5.76</v>
+        <v>5.785</v>
       </c>
       <c r="J256" t="n">
-        <v>15.18</v>
+        <v>15.115</v>
       </c>
       <c r="K256" t="n">
-        <v>2.365</v>
+        <v>2.390000000000001</v>
       </c>
       <c r="L256" t="n">
-        <v>3.395</v>
+        <v>3.465</v>
       </c>
       <c r="M256" t="n">
-        <v>300.0145777692024</v>
+        <v>264.0982794604473</v>
       </c>
       <c r="N256" t="n">
-        <v>5.445362991302629</v>
+        <v>5.252787017481772</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="B257" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C257" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="D257" t="n">
-        <v>81.1057682329695</v>
+        <v>93.41234092860827</v>
       </c>
       <c r="E257" t="n">
-        <v>465.35</v>
+        <v>471.15</v>
       </c>
       <c r="F257" t="n">
-        <v>158.2713917987254</v>
+        <v>156.3230227603457</v>
       </c>
       <c r="G257" t="n">
-        <v>53456.40773859157</v>
+        <v>6768.626139458149</v>
       </c>
       <c r="H257" t="n">
-        <v>-8709.761175251018</v>
+        <v>-1797.684294448047</v>
       </c>
       <c r="I257" t="n">
-        <v>5.76</v>
+        <v>5.785</v>
       </c>
       <c r="J257" t="n">
-        <v>15.18</v>
+        <v>15.115</v>
       </c>
       <c r="K257" t="n">
-        <v>2.365</v>
+        <v>2.390000000000001</v>
       </c>
       <c r="L257" t="n">
-        <v>3.395</v>
+        <v>3.465</v>
       </c>
       <c r="M257" t="n">
-        <v>300.0145777691984</v>
+        <v>264.0982794604473</v>
       </c>
       <c r="N257" t="n">
-        <v>5.445362991302568</v>
+        <v>5.252787017481772</v>
       </c>
     </row>
     <row r="258">
@@ -11769,7 +11769,7 @@
         <v>414</v>
       </c>
       <c r="B258" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C258" t="n">
         <v>414</v>
@@ -11813,7 +11813,7 @@
         <v>414</v>
       </c>
       <c r="B259" t="n">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C259" t="n">
         <v>414</v>
@@ -11857,7 +11857,7 @@
         <v>414</v>
       </c>
       <c r="B260" t="n">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C260" t="n">
         <v>414</v>
@@ -11901,7 +11901,7 @@
         <v>414</v>
       </c>
       <c r="B261" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C261" t="n">
         <v>414</v>
@@ -11945,43 +11945,43 @@
         <v>414</v>
       </c>
       <c r="B262" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C262" t="n">
         <v>414</v>
       </c>
       <c r="D262" t="n">
-        <v>80.5993281368212</v>
+        <v>81.10576822897893</v>
       </c>
       <c r="E262" t="n">
-        <v>462.27</v>
+        <v>465.35</v>
       </c>
       <c r="F262" t="n">
-        <v>159.3259181290953</v>
+        <v>158.2713917987254</v>
       </c>
       <c r="G262" t="n">
-        <v>55296.6551279927</v>
+        <v>53456.40773834212</v>
       </c>
       <c r="H262" t="n">
-        <v>-8941.533577596239</v>
+        <v>-8709.7611760448</v>
       </c>
       <c r="I262" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="J262" t="n">
-        <v>14.62</v>
+        <v>15.18</v>
       </c>
       <c r="K262" t="n">
-        <v>2.285</v>
+        <v>2.365</v>
       </c>
       <c r="L262" t="n">
-        <v>3.305</v>
+        <v>3.395</v>
       </c>
       <c r="M262" t="n">
-        <v>300.0306225463988</v>
+        <v>300.0145777692024</v>
       </c>
       <c r="N262" t="n">
-        <v>5.486513712400239</v>
+        <v>5.445362991302629</v>
       </c>
     </row>
     <row r="263">
@@ -11989,43 +11989,43 @@
         <v>414</v>
       </c>
       <c r="B263" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C263" t="n">
         <v>414</v>
       </c>
       <c r="D263" t="n">
-        <v>80.59932813959078</v>
+        <v>81.1057682329695</v>
       </c>
       <c r="E263" t="n">
-        <v>462.27</v>
+        <v>465.35</v>
       </c>
       <c r="F263" t="n">
-        <v>159.3259181290953</v>
+        <v>158.2713917987254</v>
       </c>
       <c r="G263" t="n">
-        <v>55296.65512740833</v>
+        <v>53456.40773859157</v>
       </c>
       <c r="H263" t="n">
-        <v>-8941.53357784768</v>
+        <v>-8709.761175251018</v>
       </c>
       <c r="I263" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="J263" t="n">
-        <v>14.62</v>
+        <v>15.18</v>
       </c>
       <c r="K263" t="n">
-        <v>2.285</v>
+        <v>2.365</v>
       </c>
       <c r="L263" t="n">
-        <v>3.305</v>
+        <v>3.395</v>
       </c>
       <c r="M263" t="n">
-        <v>300.0306225463948</v>
+        <v>300.0145777691984</v>
       </c>
       <c r="N263" t="n">
-        <v>5.486513712400239</v>
+        <v>5.445362991302568</v>
       </c>
     </row>
     <row r="264">
@@ -12033,43 +12033,43 @@
         <v>414</v>
       </c>
       <c r="B264" t="n">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C264" t="n">
         <v>414</v>
       </c>
       <c r="D264" t="n">
-        <v>80.5993281368212</v>
+        <v>81.10576822897893</v>
       </c>
       <c r="E264" t="n">
-        <v>462.27</v>
+        <v>465.35</v>
       </c>
       <c r="F264" t="n">
-        <v>159.3259181290953</v>
+        <v>158.2713917987254</v>
       </c>
       <c r="G264" t="n">
-        <v>55296.6551279927</v>
+        <v>53456.40773834212</v>
       </c>
       <c r="H264" t="n">
-        <v>-8941.533577596239</v>
+        <v>-8709.7611760448</v>
       </c>
       <c r="I264" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="J264" t="n">
-        <v>14.62</v>
+        <v>15.18</v>
       </c>
       <c r="K264" t="n">
-        <v>2.285</v>
+        <v>2.365</v>
       </c>
       <c r="L264" t="n">
-        <v>3.305</v>
+        <v>3.395</v>
       </c>
       <c r="M264" t="n">
-        <v>300.0306225463988</v>
+        <v>300.0145777692024</v>
       </c>
       <c r="N264" t="n">
-        <v>5.486513712400239</v>
+        <v>5.445362991302629</v>
       </c>
     </row>
     <row r="265">
@@ -12077,43 +12077,43 @@
         <v>414</v>
       </c>
       <c r="B265" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C265" t="n">
         <v>414</v>
       </c>
       <c r="D265" t="n">
-        <v>80.59932813959078</v>
+        <v>81.1057682329695</v>
       </c>
       <c r="E265" t="n">
-        <v>462.27</v>
+        <v>465.35</v>
       </c>
       <c r="F265" t="n">
-        <v>159.3259181290953</v>
+        <v>158.2713917987254</v>
       </c>
       <c r="G265" t="n">
-        <v>55296.65512740833</v>
+        <v>53456.40773859157</v>
       </c>
       <c r="H265" t="n">
-        <v>-8941.53357784768</v>
+        <v>-8709.761175251018</v>
       </c>
       <c r="I265" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="J265" t="n">
-        <v>14.62</v>
+        <v>15.18</v>
       </c>
       <c r="K265" t="n">
-        <v>2.285</v>
+        <v>2.365</v>
       </c>
       <c r="L265" t="n">
-        <v>3.305</v>
+        <v>3.395</v>
       </c>
       <c r="M265" t="n">
-        <v>300.0306225463948</v>
+        <v>300.0145777691984</v>
       </c>
       <c r="N265" t="n">
-        <v>5.486513712400239</v>
+        <v>5.445362991302568</v>
       </c>
     </row>
     <row r="266">
@@ -12121,7 +12121,7 @@
         <v>414</v>
       </c>
       <c r="B266" t="n">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C266" t="n">
         <v>414</v>
@@ -12165,7 +12165,7 @@
         <v>414</v>
       </c>
       <c r="B267" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C267" t="n">
         <v>414</v>
@@ -12209,7 +12209,7 @@
         <v>414</v>
       </c>
       <c r="B268" t="n">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C268" t="n">
         <v>414</v>
@@ -12253,7 +12253,7 @@
         <v>414</v>
       </c>
       <c r="B269" t="n">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C269" t="n">
         <v>414</v>
@@ -12297,43 +12297,43 @@
         <v>414</v>
       </c>
       <c r="B270" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C270" t="n">
         <v>414</v>
       </c>
       <c r="D270" t="n">
-        <v>80.08164083422861</v>
+        <v>80.5993281368212</v>
       </c>
       <c r="E270" t="n">
-        <v>459.535</v>
+        <v>462.27</v>
       </c>
       <c r="F270" t="n">
-        <v>160.274173182754</v>
+        <v>159.3259181290953</v>
       </c>
       <c r="G270" t="n">
-        <v>57143.91362510951</v>
+        <v>55296.6551279927</v>
       </c>
       <c r="H270" t="n">
-        <v>-9166.333907965825</v>
+        <v>-8941.533577596239</v>
       </c>
       <c r="I270" t="n">
-        <v>5.705</v>
+        <v>5.73</v>
       </c>
       <c r="J270" t="n">
-        <v>14.125</v>
+        <v>14.62</v>
       </c>
       <c r="K270" t="n">
-        <v>2.22</v>
+        <v>2.285</v>
       </c>
       <c r="L270" t="n">
-        <v>3.23</v>
+        <v>3.305</v>
       </c>
       <c r="M270" t="n">
-        <v>300.0454050661697</v>
+        <v>300.0306225463988</v>
       </c>
       <c r="N270" t="n">
-        <v>5.527613322486853</v>
+        <v>5.486513712400239</v>
       </c>
     </row>
     <row r="271">
@@ -12341,43 +12341,43 @@
         <v>414</v>
       </c>
       <c r="B271" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C271" t="n">
         <v>414</v>
       </c>
       <c r="D271" t="n">
-        <v>80.0481433162069</v>
+        <v>80.59932813959078</v>
       </c>
       <c r="E271" t="n">
-        <v>459.74</v>
+        <v>462.27</v>
       </c>
       <c r="F271" t="n">
-        <v>160.2027062547024</v>
+        <v>159.3259181290953</v>
       </c>
       <c r="G271" t="n">
-        <v>57216.21443155643</v>
+        <v>55296.65512740833</v>
       </c>
       <c r="H271" t="n">
-        <v>-9145.972164340303</v>
+        <v>-8941.53357784768</v>
       </c>
       <c r="I271" t="n">
-        <v>5.705</v>
+        <v>5.73</v>
       </c>
       <c r="J271" t="n">
-        <v>14.125</v>
+        <v>14.62</v>
       </c>
       <c r="K271" t="n">
-        <v>2.22</v>
+        <v>2.285</v>
       </c>
       <c r="L271" t="n">
-        <v>3.23</v>
+        <v>3.305</v>
       </c>
       <c r="M271" t="n">
-        <v>300.0454050661697</v>
+        <v>300.0306225463948</v>
       </c>
       <c r="N271" t="n">
-        <v>5.527613322486927</v>
+        <v>5.486513712400239</v>
       </c>
     </row>
     <row r="272">
@@ -12385,43 +12385,43 @@
         <v>414</v>
       </c>
       <c r="B272" t="n">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C272" t="n">
         <v>414</v>
       </c>
       <c r="D272" t="n">
-        <v>80.08164083422861</v>
+        <v>80.5993281368212</v>
       </c>
       <c r="E272" t="n">
-        <v>459.535</v>
+        <v>462.27</v>
       </c>
       <c r="F272" t="n">
-        <v>160.274173182754</v>
+        <v>159.3259181290953</v>
       </c>
       <c r="G272" t="n">
-        <v>57143.91362510951</v>
+        <v>55296.6551279927</v>
       </c>
       <c r="H272" t="n">
-        <v>-9166.333907965825</v>
+        <v>-8941.533577596239</v>
       </c>
       <c r="I272" t="n">
-        <v>5.705</v>
+        <v>5.73</v>
       </c>
       <c r="J272" t="n">
-        <v>14.125</v>
+        <v>14.62</v>
       </c>
       <c r="K272" t="n">
-        <v>2.22</v>
+        <v>2.285</v>
       </c>
       <c r="L272" t="n">
-        <v>3.23</v>
+        <v>3.305</v>
       </c>
       <c r="M272" t="n">
-        <v>300.0454050661697</v>
+        <v>300.0306225463988</v>
       </c>
       <c r="N272" t="n">
-        <v>5.527613322486853</v>
+        <v>5.486513712400239</v>
       </c>
     </row>
     <row r="273">
@@ -12429,43 +12429,43 @@
         <v>414</v>
       </c>
       <c r="B273" t="n">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C273" t="n">
         <v>414</v>
       </c>
       <c r="D273" t="n">
-        <v>80.0481433162069</v>
+        <v>80.59932813959078</v>
       </c>
       <c r="E273" t="n">
-        <v>459.74</v>
+        <v>462.27</v>
       </c>
       <c r="F273" t="n">
-        <v>160.2027062547024</v>
+        <v>159.3259181290953</v>
       </c>
       <c r="G273" t="n">
-        <v>57216.21443155643</v>
+        <v>55296.65512740833</v>
       </c>
       <c r="H273" t="n">
-        <v>-9145.972164340303</v>
+        <v>-8941.53357784768</v>
       </c>
       <c r="I273" t="n">
-        <v>5.705</v>
+        <v>5.73</v>
       </c>
       <c r="J273" t="n">
-        <v>14.125</v>
+        <v>14.62</v>
       </c>
       <c r="K273" t="n">
-        <v>2.22</v>
+        <v>2.285</v>
       </c>
       <c r="L273" t="n">
-        <v>3.23</v>
+        <v>3.305</v>
       </c>
       <c r="M273" t="n">
-        <v>300.0454050661697</v>
+        <v>300.0306225463948</v>
       </c>
       <c r="N273" t="n">
-        <v>5.527613322486927</v>
+        <v>5.486513712400239</v>
       </c>
     </row>
     <row r="274">
@@ -12473,7 +12473,7 @@
         <v>414</v>
       </c>
       <c r="B274" t="n">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C274" t="n">
         <v>414</v>
@@ -12517,7 +12517,7 @@
         <v>414</v>
       </c>
       <c r="B275" t="n">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C275" t="n">
         <v>414</v>
@@ -12561,7 +12561,7 @@
         <v>414</v>
       </c>
       <c r="B276" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C276" t="n">
         <v>414</v>
@@ -12605,7 +12605,7 @@
         <v>414</v>
       </c>
       <c r="B277" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C277" t="n">
         <v>414</v>
@@ -12649,43 +12649,43 @@
         <v>414</v>
       </c>
       <c r="B278" t="n">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C278" t="n">
         <v>414</v>
       </c>
       <c r="D278" t="n">
-        <v>79.52637398021875</v>
+        <v>80.08164083422861</v>
       </c>
       <c r="E278" t="n">
-        <v>457.285</v>
+        <v>459.535</v>
       </c>
       <c r="F278" t="n">
-        <v>161.0627774222571</v>
+        <v>160.274173182754</v>
       </c>
       <c r="G278" t="n">
-        <v>59058.53259269777</v>
+        <v>57143.91362510951</v>
       </c>
       <c r="H278" t="n">
-        <v>-9373.290354781193</v>
+        <v>-9166.333907965825</v>
       </c>
       <c r="I278" t="n">
-        <v>5.68</v>
+        <v>5.705</v>
       </c>
       <c r="J278" t="n">
-        <v>13.7</v>
+        <v>14.125</v>
       </c>
       <c r="K278" t="n">
-        <v>2.175</v>
+        <v>2.22</v>
       </c>
       <c r="L278" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="M278" t="n">
-        <v>300.0591173385881</v>
+        <v>300.0454050661697</v>
       </c>
       <c r="N278" t="n">
-        <v>5.568655435900878</v>
+        <v>5.527613322486853</v>
       </c>
     </row>
     <row r="279">
@@ -12693,43 +12693,43 @@
         <v>414</v>
       </c>
       <c r="B279" t="n">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C279" t="n">
         <v>414</v>
       </c>
       <c r="D279" t="n">
-        <v>79.52429889271406</v>
+        <v>80.0481433162069</v>
       </c>
       <c r="E279" t="n">
-        <v>457.295</v>
+        <v>459.74</v>
       </c>
       <c r="F279" t="n">
-        <v>161.059255346192</v>
+        <v>160.2027062547024</v>
       </c>
       <c r="G279" t="n">
-        <v>59063.27492196056</v>
+        <v>57216.21443155643</v>
       </c>
       <c r="H279" t="n">
-        <v>-9372.369234970662</v>
+        <v>-9145.972164340303</v>
       </c>
       <c r="I279" t="n">
-        <v>5.68</v>
+        <v>5.705</v>
       </c>
       <c r="J279" t="n">
-        <v>13.7</v>
+        <v>14.125</v>
       </c>
       <c r="K279" t="n">
-        <v>2.175</v>
+        <v>2.22</v>
       </c>
       <c r="L279" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="M279" t="n">
-        <v>300.0591173385874</v>
+        <v>300.0454050661697</v>
       </c>
       <c r="N279" t="n">
-        <v>5.568655435900948</v>
+        <v>5.527613322486927</v>
       </c>
     </row>
     <row r="280">
@@ -12737,43 +12737,43 @@
         <v>414</v>
       </c>
       <c r="B280" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C280" t="n">
         <v>414</v>
       </c>
       <c r="D280" t="n">
-        <v>79.52637398021875</v>
+        <v>80.08164083422861</v>
       </c>
       <c r="E280" t="n">
-        <v>457.285</v>
+        <v>459.535</v>
       </c>
       <c r="F280" t="n">
-        <v>161.0627774222571</v>
+        <v>160.274173182754</v>
       </c>
       <c r="G280" t="n">
-        <v>59058.53259269777</v>
+        <v>57143.91362510951</v>
       </c>
       <c r="H280" t="n">
-        <v>-9373.290354781193</v>
+        <v>-9166.333907965825</v>
       </c>
       <c r="I280" t="n">
-        <v>5.68</v>
+        <v>5.705</v>
       </c>
       <c r="J280" t="n">
-        <v>13.7</v>
+        <v>14.125</v>
       </c>
       <c r="K280" t="n">
-        <v>2.175</v>
+        <v>2.22</v>
       </c>
       <c r="L280" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="M280" t="n">
-        <v>300.0591173385881</v>
+        <v>300.0454050661697</v>
       </c>
       <c r="N280" t="n">
-        <v>5.568655435900878</v>
+        <v>5.527613322486853</v>
       </c>
     </row>
     <row r="281">
@@ -12781,43 +12781,43 @@
         <v>414</v>
       </c>
       <c r="B281" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C281" t="n">
         <v>414</v>
       </c>
       <c r="D281" t="n">
-        <v>79.52429889271406</v>
+        <v>80.0481433162069</v>
       </c>
       <c r="E281" t="n">
-        <v>457.295</v>
+        <v>459.74</v>
       </c>
       <c r="F281" t="n">
-        <v>161.059255346192</v>
+        <v>160.2027062547024</v>
       </c>
       <c r="G281" t="n">
-        <v>59063.27492196056</v>
+        <v>57216.21443155643</v>
       </c>
       <c r="H281" t="n">
-        <v>-9372.369234970662</v>
+        <v>-9145.972164340303</v>
       </c>
       <c r="I281" t="n">
-        <v>5.68</v>
+        <v>5.705</v>
       </c>
       <c r="J281" t="n">
-        <v>13.7</v>
+        <v>14.125</v>
       </c>
       <c r="K281" t="n">
-        <v>2.175</v>
+        <v>2.22</v>
       </c>
       <c r="L281" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="M281" t="n">
-        <v>300.0591173385874</v>
+        <v>300.0454050661697</v>
       </c>
       <c r="N281" t="n">
-        <v>5.568655435900948</v>
+        <v>5.527613322486927</v>
       </c>
     </row>
     <row r="282">
@@ -12825,7 +12825,7 @@
         <v>414</v>
       </c>
       <c r="B282" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C282" t="n">
         <v>414</v>
@@ -12869,7 +12869,7 @@
         <v>414</v>
       </c>
       <c r="B283" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C283" t="n">
         <v>414</v>
@@ -12913,7 +12913,7 @@
         <v>414</v>
       </c>
       <c r="B284" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C284" t="n">
         <v>414</v>
@@ -12957,7 +12957,7 @@
         <v>414</v>
       </c>
       <c r="B285" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C285" t="n">
         <v>414</v>
@@ -12993,6 +12993,182 @@
         <v>300.0591173385874</v>
       </c>
       <c r="N285" t="n">
+        <v>5.568655435900948</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>414</v>
+      </c>
+      <c r="B286" t="n">
+        <v>285</v>
+      </c>
+      <c r="C286" t="n">
+        <v>414</v>
+      </c>
+      <c r="D286" t="n">
+        <v>79.52637398021875</v>
+      </c>
+      <c r="E286" t="n">
+        <v>457.285</v>
+      </c>
+      <c r="F286" t="n">
+        <v>161.0627774222571</v>
+      </c>
+      <c r="G286" t="n">
+        <v>59058.53259269777</v>
+      </c>
+      <c r="H286" t="n">
+        <v>-9373.290354781193</v>
+      </c>
+      <c r="I286" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J286" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K286" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="L286" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M286" t="n">
+        <v>300.0591173385881</v>
+      </c>
+      <c r="N286" t="n">
+        <v>5.568655435900878</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>414</v>
+      </c>
+      <c r="B287" t="n">
+        <v>286</v>
+      </c>
+      <c r="C287" t="n">
+        <v>414</v>
+      </c>
+      <c r="D287" t="n">
+        <v>79.52429889271406</v>
+      </c>
+      <c r="E287" t="n">
+        <v>457.295</v>
+      </c>
+      <c r="F287" t="n">
+        <v>161.059255346192</v>
+      </c>
+      <c r="G287" t="n">
+        <v>59063.27492196056</v>
+      </c>
+      <c r="H287" t="n">
+        <v>-9372.369234970662</v>
+      </c>
+      <c r="I287" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J287" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K287" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="L287" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M287" t="n">
+        <v>300.0591173385874</v>
+      </c>
+      <c r="N287" t="n">
+        <v>5.568655435900948</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>414</v>
+      </c>
+      <c r="B288" t="n">
+        <v>287</v>
+      </c>
+      <c r="C288" t="n">
+        <v>414</v>
+      </c>
+      <c r="D288" t="n">
+        <v>79.52637398021875</v>
+      </c>
+      <c r="E288" t="n">
+        <v>457.285</v>
+      </c>
+      <c r="F288" t="n">
+        <v>161.0627774222571</v>
+      </c>
+      <c r="G288" t="n">
+        <v>59058.53259269777</v>
+      </c>
+      <c r="H288" t="n">
+        <v>-9373.290354781193</v>
+      </c>
+      <c r="I288" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J288" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K288" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="L288" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M288" t="n">
+        <v>300.0591173385881</v>
+      </c>
+      <c r="N288" t="n">
+        <v>5.568655435900878</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>414</v>
+      </c>
+      <c r="B289" t="n">
+        <v>288</v>
+      </c>
+      <c r="C289" t="n">
+        <v>414</v>
+      </c>
+      <c r="D289" t="n">
+        <v>79.52429889271406</v>
+      </c>
+      <c r="E289" t="n">
+        <v>457.295</v>
+      </c>
+      <c r="F289" t="n">
+        <v>161.059255346192</v>
+      </c>
+      <c r="G289" t="n">
+        <v>59063.27492196056</v>
+      </c>
+      <c r="H289" t="n">
+        <v>-9372.369234970662</v>
+      </c>
+      <c r="I289" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J289" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K289" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="L289" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M289" t="n">
+        <v>300.0591173385874</v>
+      </c>
+      <c r="N289" t="n">
         <v>5.568655435900948</v>
       </c>
     </row>
